--- a/Customer Rate Tariff Template_Week 31_2026.xlsx
+++ b/Customer Rate Tariff Template_Week 31_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stephanie.galera.RAMPSLOGISTICS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98240CE-D011-4A71-8323-CD0BB176A5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412D248C-C6ED-4917-8CD3-E731EAEAA4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{493693A0-0616-4273-B364-7C8DEB21885C}"/>
   </bookViews>
@@ -2263,6 +2263,60 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2280,6 +2334,105 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2311,164 +2464,56 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2506,63 +2551,68 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2577,62 +2627,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2645,20 +2639,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2684,8 +2669,23 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4146,23 +4146,23 @@
       <c r="P7" s="18"/>
     </row>
     <row r="8" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="249" t="s">
+      <c r="B8" s="223" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="249"/>
-      <c r="D8" s="249"/>
-      <c r="E8" s="249"/>
-      <c r="F8" s="249"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="249"/>
-      <c r="K8" s="249"/>
-      <c r="L8" s="249"/>
-      <c r="M8" s="249"/>
-      <c r="N8" s="249"/>
-      <c r="O8" s="249"/>
-      <c r="P8" s="249"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="223"/>
+      <c r="H8" s="223"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="223"/>
+      <c r="K8" s="223"/>
+      <c r="L8" s="223"/>
+      <c r="M8" s="223"/>
+      <c r="N8" s="223"/>
+      <c r="O8" s="223"/>
+      <c r="P8" s="223"/>
     </row>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
@@ -4210,10 +4210,10 @@
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="283" t="s">
+      <c r="B10" s="224" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="283" t="s">
+      <c r="C10" s="224" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="20" t="s">
@@ -4259,8 +4259,8 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="284"/>
-      <c r="C11" s="284"/>
+      <c r="B11" s="225"/>
+      <c r="C11" s="225"/>
       <c r="D11" s="20" t="s">
         <v>22</v>
       </c>
@@ -4304,8 +4304,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="284"/>
-      <c r="C12" s="283" t="s">
+      <c r="B12" s="225"/>
+      <c r="C12" s="224" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="111" t="s">
@@ -4352,8 +4352,8 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="284"/>
-      <c r="C13" s="284"/>
+      <c r="B13" s="225"/>
+      <c r="C13" s="225"/>
       <c r="D13" s="111" t="s">
         <v>22</v>
       </c>
@@ -4399,10 +4399,10 @@
       <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="285" t="s">
+      <c r="B14" s="226" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="237" t="s">
+      <c r="C14" s="228" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -4449,8 +4449,8 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="286"/>
-      <c r="C15" s="237"/>
+      <c r="B15" s="227"/>
+      <c r="C15" s="228"/>
       <c r="D15" s="20" t="s">
         <v>22</v>
       </c>
@@ -4495,10 +4495,10 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="285" t="s">
+      <c r="B16" s="226" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="285" t="s">
+      <c r="C16" s="226" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -4545,8 +4545,8 @@
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="286"/>
-      <c r="C17" s="286"/>
+      <c r="B17" s="227"/>
+      <c r="C17" s="227"/>
       <c r="D17" s="20" t="s">
         <v>22</v>
       </c>
@@ -4591,10 +4591,10 @@
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="285" t="s">
+      <c r="B18" s="226" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="237" t="s">
+      <c r="C18" s="228" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -4642,8 +4642,8 @@
       <c r="Q18" s="26"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="289"/>
-      <c r="C19" s="237"/>
+      <c r="B19" s="237"/>
+      <c r="C19" s="228"/>
       <c r="D19" s="20" t="s">
         <v>22</v>
       </c>
@@ -4689,8 +4689,8 @@
       <c r="Q19" s="26"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="289"/>
-      <c r="C20" s="237" t="s">
+      <c r="B20" s="237"/>
+      <c r="C20" s="228" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -4737,8 +4737,8 @@
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="286"/>
-      <c r="C21" s="237"/>
+      <c r="B21" s="227"/>
+      <c r="C21" s="228"/>
       <c r="D21" s="20" t="s">
         <v>22</v>
       </c>
@@ -4820,74 +4820,74 @@
       <c r="P23" s="189"/>
     </row>
     <row r="24" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="280" t="s">
+      <c r="B24" s="238" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="280"/>
-      <c r="D24" s="280"/>
-      <c r="E24" s="280"/>
-      <c r="F24" s="280"/>
-      <c r="G24" s="280"/>
-      <c r="H24" s="280"/>
-      <c r="I24" s="280"/>
-      <c r="J24" s="280"/>
-      <c r="K24" s="280"/>
-      <c r="L24" s="280"/>
-      <c r="M24" s="280"/>
-      <c r="N24" s="280"/>
-      <c r="O24" s="280"/>
-      <c r="P24" s="280"/>
+      <c r="C24" s="238"/>
+      <c r="D24" s="238"/>
+      <c r="E24" s="238"/>
+      <c r="F24" s="238"/>
+      <c r="G24" s="238"/>
+      <c r="H24" s="238"/>
+      <c r="I24" s="238"/>
+      <c r="J24" s="238"/>
+      <c r="K24" s="238"/>
+      <c r="L24" s="238"/>
+      <c r="M24" s="238"/>
+      <c r="N24" s="238"/>
+      <c r="O24" s="238"/>
+      <c r="P24" s="238"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B25" s="280"/>
-      <c r="C25" s="280"/>
-      <c r="D25" s="280"/>
-      <c r="E25" s="280"/>
-      <c r="F25" s="280"/>
-      <c r="G25" s="280"/>
-      <c r="H25" s="280"/>
-      <c r="I25" s="280"/>
-      <c r="J25" s="280"/>
-      <c r="K25" s="280"/>
-      <c r="L25" s="280"/>
-      <c r="M25" s="280"/>
-      <c r="N25" s="280"/>
-      <c r="O25" s="280"/>
-      <c r="P25" s="280"/>
+      <c r="B25" s="238"/>
+      <c r="C25" s="238"/>
+      <c r="D25" s="238"/>
+      <c r="E25" s="238"/>
+      <c r="F25" s="238"/>
+      <c r="G25" s="238"/>
+      <c r="H25" s="238"/>
+      <c r="I25" s="238"/>
+      <c r="J25" s="238"/>
+      <c r="K25" s="238"/>
+      <c r="L25" s="238"/>
+      <c r="M25" s="238"/>
+      <c r="N25" s="238"/>
+      <c r="O25" s="238"/>
+      <c r="P25" s="238"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B26" s="280"/>
-      <c r="C26" s="280"/>
-      <c r="D26" s="280"/>
-      <c r="E26" s="280"/>
-      <c r="F26" s="280"/>
-      <c r="G26" s="280"/>
-      <c r="H26" s="280"/>
-      <c r="I26" s="280"/>
-      <c r="J26" s="280"/>
-      <c r="K26" s="280"/>
-      <c r="L26" s="280"/>
-      <c r="M26" s="280"/>
-      <c r="N26" s="280"/>
-      <c r="O26" s="280"/>
-      <c r="P26" s="280"/>
+      <c r="B26" s="238"/>
+      <c r="C26" s="238"/>
+      <c r="D26" s="238"/>
+      <c r="E26" s="238"/>
+      <c r="F26" s="238"/>
+      <c r="G26" s="238"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="238"/>
+      <c r="J26" s="238"/>
+      <c r="K26" s="238"/>
+      <c r="L26" s="238"/>
+      <c r="M26" s="238"/>
+      <c r="N26" s="238"/>
+      <c r="O26" s="238"/>
+      <c r="P26" s="238"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="280"/>
-      <c r="C27" s="280"/>
-      <c r="D27" s="280"/>
-      <c r="E27" s="280"/>
-      <c r="F27" s="280"/>
-      <c r="G27" s="280"/>
-      <c r="H27" s="280"/>
-      <c r="I27" s="280"/>
-      <c r="J27" s="280"/>
-      <c r="K27" s="280"/>
-      <c r="L27" s="280"/>
-      <c r="M27" s="280"/>
-      <c r="N27" s="280"/>
-      <c r="O27" s="280"/>
-      <c r="P27" s="280"/>
+      <c r="B27" s="238"/>
+      <c r="C27" s="238"/>
+      <c r="D27" s="238"/>
+      <c r="E27" s="238"/>
+      <c r="F27" s="238"/>
+      <c r="G27" s="238"/>
+      <c r="H27" s="238"/>
+      <c r="I27" s="238"/>
+      <c r="J27" s="238"/>
+      <c r="K27" s="238"/>
+      <c r="L27" s="238"/>
+      <c r="M27" s="238"/>
+      <c r="N27" s="238"/>
+      <c r="O27" s="238"/>
+      <c r="P27" s="238"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="35"/>
@@ -5016,23 +5016,23 @@
       <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="287" t="s">
+      <c r="B35" s="229" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="251"/>
-      <c r="D35" s="251"/>
-      <c r="E35" s="251"/>
-      <c r="F35" s="251"/>
-      <c r="G35" s="251"/>
-      <c r="H35" s="251"/>
-      <c r="I35" s="251"/>
-      <c r="J35" s="251"/>
-      <c r="K35" s="251"/>
-      <c r="L35" s="251"/>
-      <c r="M35" s="251"/>
-      <c r="N35" s="251"/>
-      <c r="O35" s="251"/>
-      <c r="P35" s="251"/>
+      <c r="C35" s="230"/>
+      <c r="D35" s="230"/>
+      <c r="E35" s="230"/>
+      <c r="F35" s="230"/>
+      <c r="G35" s="230"/>
+      <c r="H35" s="230"/>
+      <c r="I35" s="230"/>
+      <c r="J35" s="230"/>
+      <c r="K35" s="230"/>
+      <c r="L35" s="230"/>
+      <c r="M35" s="230"/>
+      <c r="N35" s="230"/>
+      <c r="O35" s="230"/>
+      <c r="P35" s="230"/>
     </row>
     <row r="36" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="120" t="s">
@@ -5078,7 +5078,7 @@
       <c r="P36" s="218"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B37" s="288" t="s">
+      <c r="B37" s="231" t="s">
         <v>37</v>
       </c>
       <c r="C37" s="136" t="s">
@@ -5120,13 +5120,13 @@
       <c r="N37" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O37" s="262" t="s">
+      <c r="O37" s="232" t="s">
         <v>40</v>
       </c>
-      <c r="P37" s="263"/>
+      <c r="P37" s="233"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B38" s="288"/>
+      <c r="B38" s="231"/>
       <c r="C38" s="136" t="s">
         <v>16</v>
       </c>
@@ -5166,8 +5166,8 @@
       <c r="N38" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O38" s="266"/>
-      <c r="P38" s="267"/>
+      <c r="O38" s="234"/>
+      <c r="P38" s="235"/>
     </row>
     <row r="39" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="190" t="s">
@@ -5212,10 +5212,10 @@
       <c r="N39" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O39" s="238" t="s">
+      <c r="O39" s="236" t="s">
         <v>44</v>
       </c>
-      <c r="P39" s="238"/>
+      <c r="P39" s="236"/>
     </row>
     <row r="40" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="190" t="s">
@@ -5260,10 +5260,10 @@
       <c r="N40" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O40" s="238" t="s">
+      <c r="O40" s="236" t="s">
         <v>44</v>
       </c>
-      <c r="P40" s="238"/>
+      <c r="P40" s="236"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B41" s="42"/>
@@ -5304,78 +5304,78 @@
       <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="221" t="s">
+      <c r="B43" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="222"/>
-      <c r="D43" s="222"/>
-      <c r="E43" s="222"/>
-      <c r="F43" s="222"/>
-      <c r="G43" s="222"/>
-      <c r="H43" s="222"/>
-      <c r="I43" s="222"/>
-      <c r="J43" s="222"/>
-      <c r="K43" s="222"/>
-      <c r="L43" s="222"/>
-      <c r="M43" s="222"/>
-      <c r="N43" s="222"/>
-      <c r="O43" s="222"/>
-      <c r="P43" s="222"/>
-      <c r="Q43" s="223"/>
+      <c r="C43" s="240"/>
+      <c r="D43" s="240"/>
+      <c r="E43" s="240"/>
+      <c r="F43" s="240"/>
+      <c r="G43" s="240"/>
+      <c r="H43" s="240"/>
+      <c r="I43" s="240"/>
+      <c r="J43" s="240"/>
+      <c r="K43" s="240"/>
+      <c r="L43" s="240"/>
+      <c r="M43" s="240"/>
+      <c r="N43" s="240"/>
+      <c r="O43" s="240"/>
+      <c r="P43" s="240"/>
+      <c r="Q43" s="241"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B44" s="221"/>
-      <c r="C44" s="222"/>
-      <c r="D44" s="222"/>
-      <c r="E44" s="222"/>
-      <c r="F44" s="222"/>
-      <c r="G44" s="222"/>
-      <c r="H44" s="222"/>
-      <c r="I44" s="222"/>
-      <c r="J44" s="222"/>
-      <c r="K44" s="222"/>
-      <c r="L44" s="222"/>
-      <c r="M44" s="222"/>
-      <c r="N44" s="222"/>
-      <c r="O44" s="222"/>
-      <c r="P44" s="222"/>
-      <c r="Q44" s="223"/>
+      <c r="B44" s="239"/>
+      <c r="C44" s="240"/>
+      <c r="D44" s="240"/>
+      <c r="E44" s="240"/>
+      <c r="F44" s="240"/>
+      <c r="G44" s="240"/>
+      <c r="H44" s="240"/>
+      <c r="I44" s="240"/>
+      <c r="J44" s="240"/>
+      <c r="K44" s="240"/>
+      <c r="L44" s="240"/>
+      <c r="M44" s="240"/>
+      <c r="N44" s="240"/>
+      <c r="O44" s="240"/>
+      <c r="P44" s="240"/>
+      <c r="Q44" s="241"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="221"/>
-      <c r="C45" s="222"/>
-      <c r="D45" s="222"/>
-      <c r="E45" s="222"/>
-      <c r="F45" s="222"/>
-      <c r="G45" s="222"/>
-      <c r="H45" s="222"/>
-      <c r="I45" s="222"/>
-      <c r="J45" s="222"/>
-      <c r="K45" s="222"/>
-      <c r="L45" s="222"/>
-      <c r="M45" s="222"/>
-      <c r="N45" s="222"/>
-      <c r="O45" s="222"/>
-      <c r="P45" s="222"/>
-      <c r="Q45" s="223"/>
+      <c r="B45" s="239"/>
+      <c r="C45" s="240"/>
+      <c r="D45" s="240"/>
+      <c r="E45" s="240"/>
+      <c r="F45" s="240"/>
+      <c r="G45" s="240"/>
+      <c r="H45" s="240"/>
+      <c r="I45" s="240"/>
+      <c r="J45" s="240"/>
+      <c r="K45" s="240"/>
+      <c r="L45" s="240"/>
+      <c r="M45" s="240"/>
+      <c r="N45" s="240"/>
+      <c r="O45" s="240"/>
+      <c r="P45" s="240"/>
+      <c r="Q45" s="241"/>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B46" s="224"/>
-      <c r="C46" s="225"/>
-      <c r="D46" s="225"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
-      <c r="G46" s="225"/>
-      <c r="H46" s="225"/>
-      <c r="I46" s="225"/>
-      <c r="J46" s="225"/>
-      <c r="K46" s="225"/>
-      <c r="L46" s="225"/>
-      <c r="M46" s="225"/>
-      <c r="N46" s="225"/>
-      <c r="O46" s="225"/>
-      <c r="P46" s="225"/>
-      <c r="Q46" s="226"/>
+      <c r="B46" s="242"/>
+      <c r="C46" s="243"/>
+      <c r="D46" s="243"/>
+      <c r="E46" s="243"/>
+      <c r="F46" s="243"/>
+      <c r="G46" s="243"/>
+      <c r="H46" s="243"/>
+      <c r="I46" s="243"/>
+      <c r="J46" s="243"/>
+      <c r="K46" s="243"/>
+      <c r="L46" s="243"/>
+      <c r="M46" s="243"/>
+      <c r="N46" s="243"/>
+      <c r="O46" s="243"/>
+      <c r="P46" s="243"/>
+      <c r="Q46" s="244"/>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B47" s="35"/>
@@ -5560,7 +5560,7 @@
       <c r="P56" s="217"/>
       <c r="Q56" s="217"/>
       <c r="R56" s="217"/>
-      <c r="S56" s="239"/>
+      <c r="S56" s="245"/>
     </row>
     <row r="57" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
@@ -5609,16 +5609,16 @@
       <c r="Q57" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R57" s="281" t="s">
+      <c r="R57" s="246" t="s">
         <v>36</v>
       </c>
-      <c r="S57" s="282"/>
+      <c r="S57" s="247"/>
     </row>
     <row r="58" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="243" t="s">
+      <c r="B58" s="248" t="s">
         <v>51</v>
       </c>
-      <c r="C58" s="244" t="s">
+      <c r="C58" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D58" s="137" t="s">
@@ -5666,14 +5666,14 @@
       <c r="Q58" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R58" s="245" t="s">
+      <c r="R58" s="250" t="s">
         <v>55</v>
       </c>
-      <c r="S58" s="246"/>
+      <c r="S58" s="251"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B59" s="243"/>
-      <c r="C59" s="244"/>
+      <c r="B59" s="248"/>
+      <c r="C59" s="249"/>
       <c r="D59" s="137" t="s">
         <v>22</v>
       </c>
@@ -5719,14 +5719,14 @@
       <c r="Q59" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R59" s="247"/>
-      <c r="S59" s="248"/>
+      <c r="R59" s="252"/>
+      <c r="S59" s="253"/>
     </row>
     <row r="60" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="243" t="s">
+      <c r="B60" s="248" t="s">
         <v>56</v>
       </c>
-      <c r="C60" s="244" t="s">
+      <c r="C60" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="137" t="s">
@@ -5774,12 +5774,12 @@
       <c r="Q60" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R60" s="247"/>
-      <c r="S60" s="248"/>
+      <c r="R60" s="252"/>
+      <c r="S60" s="253"/>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B61" s="243"/>
-      <c r="C61" s="244"/>
+      <c r="B61" s="248"/>
+      <c r="C61" s="249"/>
       <c r="D61" s="137" t="s">
         <v>22</v>
       </c>
@@ -5825,14 +5825,14 @@
       <c r="Q61" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R61" s="259"/>
-      <c r="S61" s="260"/>
+      <c r="R61" s="254"/>
+      <c r="S61" s="255"/>
     </row>
     <row r="62" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="268" t="s">
+      <c r="B62" s="261" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="253" t="s">
+      <c r="C62" s="221" t="s">
         <v>29</v>
       </c>
       <c r="D62" s="117" t="s">
@@ -5880,14 +5880,14 @@
       <c r="Q62" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R62" s="262" t="s">
+      <c r="R62" s="232" t="s">
         <v>59</v>
       </c>
-      <c r="S62" s="263"/>
+      <c r="S62" s="233"/>
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B63" s="269"/>
-      <c r="C63" s="270"/>
+      <c r="B63" s="262"/>
+      <c r="C63" s="222"/>
       <c r="D63" s="117" t="s">
         <v>22</v>
       </c>
@@ -5933,14 +5933,14 @@
       <c r="Q63" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R63" s="266"/>
-      <c r="S63" s="267"/>
+      <c r="R63" s="234"/>
+      <c r="S63" s="235"/>
     </row>
     <row r="64" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="243" t="s">
+      <c r="B64" s="248" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="244" t="s">
+      <c r="C64" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D64" s="137" t="s">
@@ -5988,14 +5988,14 @@
       <c r="Q64" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R64" s="245" t="s">
+      <c r="R64" s="250" t="s">
         <v>55</v>
       </c>
-      <c r="S64" s="246"/>
+      <c r="S64" s="251"/>
     </row>
     <row r="65" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B65" s="243"/>
-      <c r="C65" s="244"/>
+      <c r="B65" s="248"/>
+      <c r="C65" s="249"/>
       <c r="D65" s="137" t="s">
         <v>22</v>
       </c>
@@ -6041,14 +6041,14 @@
       <c r="Q65" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R65" s="247"/>
-      <c r="S65" s="248"/>
+      <c r="R65" s="252"/>
+      <c r="S65" s="253"/>
     </row>
     <row r="66" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="268" t="s">
+      <c r="B66" s="261" t="s">
         <v>61</v>
       </c>
-      <c r="C66" s="253" t="s">
+      <c r="C66" s="221" t="s">
         <v>29</v>
       </c>
       <c r="D66" s="117" t="s">
@@ -6096,14 +6096,14 @@
       <c r="Q66" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R66" s="262" t="s">
+      <c r="R66" s="232" t="s">
         <v>59</v>
       </c>
-      <c r="S66" s="263"/>
+      <c r="S66" s="233"/>
     </row>
     <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="269"/>
-      <c r="C67" s="270"/>
+      <c r="B67" s="262"/>
+      <c r="C67" s="222"/>
       <c r="D67" s="117" t="s">
         <v>22</v>
       </c>
@@ -6149,14 +6149,14 @@
       <c r="Q67" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="R67" s="266"/>
-      <c r="S67" s="267"/>
+      <c r="R67" s="234"/>
+      <c r="S67" s="235"/>
     </row>
     <row r="68" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B68" s="274" t="s">
+      <c r="B68" s="266" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="244" t="s">
+      <c r="C68" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D68" s="137" t="s">
@@ -6204,14 +6204,14 @@
       <c r="Q68" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R68" s="245" t="s">
+      <c r="R68" s="250" t="s">
         <v>55</v>
       </c>
-      <c r="S68" s="246"/>
+      <c r="S68" s="251"/>
     </row>
     <row r="69" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B69" s="275"/>
-      <c r="C69" s="244"/>
+      <c r="B69" s="267"/>
+      <c r="C69" s="249"/>
       <c r="D69" s="137" t="s">
         <v>22</v>
       </c>
@@ -6257,14 +6257,14 @@
       <c r="Q69" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R69" s="247"/>
-      <c r="S69" s="248"/>
+      <c r="R69" s="252"/>
+      <c r="S69" s="253"/>
     </row>
     <row r="70" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="243" t="s">
+      <c r="B70" s="248" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="244" t="s">
+      <c r="C70" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D70" s="137" t="s">
@@ -6312,12 +6312,12 @@
       <c r="Q70" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R70" s="247"/>
-      <c r="S70" s="248"/>
+      <c r="R70" s="252"/>
+      <c r="S70" s="253"/>
     </row>
     <row r="71" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B71" s="243"/>
-      <c r="C71" s="244"/>
+      <c r="B71" s="248"/>
+      <c r="C71" s="249"/>
       <c r="D71" s="137" t="s">
         <v>22</v>
       </c>
@@ -6363,14 +6363,14 @@
       <c r="Q71" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R71" s="259"/>
-      <c r="S71" s="260"/>
+      <c r="R71" s="254"/>
+      <c r="S71" s="255"/>
     </row>
     <row r="72" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B72" s="271" t="s">
+      <c r="B72" s="263" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="272" t="s">
+      <c r="C72" s="264" t="s">
         <v>29</v>
       </c>
       <c r="D72" s="182" t="s">
@@ -6418,14 +6418,14 @@
       <c r="Q72" s="184" t="s">
         <v>65</v>
       </c>
-      <c r="R72" s="254" t="s">
+      <c r="R72" s="257" t="s">
         <v>66</v>
       </c>
-      <c r="S72" s="255"/>
+      <c r="S72" s="258"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B73" s="271"/>
-      <c r="C73" s="273"/>
+      <c r="B73" s="263"/>
+      <c r="C73" s="265"/>
       <c r="D73" s="182" t="s">
         <v>22</v>
       </c>
@@ -6471,14 +6471,14 @@
       <c r="Q73" s="184" t="s">
         <v>65</v>
       </c>
-      <c r="R73" s="256"/>
-      <c r="S73" s="257"/>
+      <c r="R73" s="259"/>
+      <c r="S73" s="260"/>
     </row>
     <row r="74" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="243" t="s">
+      <c r="B74" s="248" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="244" t="s">
+      <c r="C74" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="137" t="s">
@@ -6526,14 +6526,14 @@
       <c r="Q74" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R74" s="245" t="s">
+      <c r="R74" s="250" t="s">
         <v>55</v>
       </c>
-      <c r="S74" s="246"/>
+      <c r="S74" s="251"/>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B75" s="243"/>
-      <c r="C75" s="244"/>
+      <c r="B75" s="248"/>
+      <c r="C75" s="249"/>
       <c r="D75" s="137" t="s">
         <v>22</v>
       </c>
@@ -6579,14 +6579,14 @@
       <c r="Q75" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R75" s="247"/>
-      <c r="S75" s="248"/>
+      <c r="R75" s="252"/>
+      <c r="S75" s="253"/>
     </row>
     <row r="76" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="243" t="s">
+      <c r="B76" s="248" t="s">
         <v>68</v>
       </c>
-      <c r="C76" s="244" t="s">
+      <c r="C76" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D76" s="137" t="s">
@@ -6634,12 +6634,12 @@
       <c r="Q76" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R76" s="247"/>
-      <c r="S76" s="248"/>
+      <c r="R76" s="252"/>
+      <c r="S76" s="253"/>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B77" s="243"/>
-      <c r="C77" s="244"/>
+      <c r="B77" s="248"/>
+      <c r="C77" s="249"/>
       <c r="D77" s="137" t="s">
         <v>22</v>
       </c>
@@ -6685,14 +6685,14 @@
       <c r="Q77" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R77" s="247"/>
-      <c r="S77" s="248"/>
+      <c r="R77" s="252"/>
+      <c r="S77" s="253"/>
     </row>
     <row r="78" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="243" t="s">
+      <c r="B78" s="248" t="s">
         <v>69</v>
       </c>
-      <c r="C78" s="244" t="s">
+      <c r="C78" s="249" t="s">
         <v>52</v>
       </c>
       <c r="D78" s="137" t="s">
@@ -6740,12 +6740,12 @@
       <c r="Q78" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R78" s="247"/>
-      <c r="S78" s="248"/>
+      <c r="R78" s="252"/>
+      <c r="S78" s="253"/>
     </row>
     <row r="79" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="243"/>
-      <c r="C79" s="244"/>
+      <c r="B79" s="248"/>
+      <c r="C79" s="249"/>
       <c r="D79" s="137" t="s">
         <v>22</v>
       </c>
@@ -6791,8 +6791,8 @@
       <c r="Q79" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R79" s="259"/>
-      <c r="S79" s="260"/>
+      <c r="R79" s="254"/>
+      <c r="S79" s="255"/>
     </row>
     <row r="80" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B80" s="216" t="s">
@@ -6813,17 +6813,17 @@
       <c r="O80" s="217"/>
       <c r="P80" s="217"/>
       <c r="Q80" s="217"/>
-      <c r="R80" s="249"/>
-      <c r="S80" s="258"/>
+      <c r="R80" s="223"/>
+      <c r="S80" s="272"/>
     </row>
     <row r="81" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B81" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="240" t="s">
+      <c r="C81" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D81" s="241"/>
+      <c r="D81" s="274"/>
       <c r="E81" s="120" t="s">
         <v>3</v>
       </c>
@@ -6863,16 +6863,16 @@
       <c r="Q81" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R81" s="240" t="s">
+      <c r="R81" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S81" s="242"/>
+      <c r="S81" s="275"/>
     </row>
     <row r="82" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="276" t="s">
+      <c r="B82" s="268" t="s">
         <v>71</v>
       </c>
-      <c r="C82" s="278" t="s">
+      <c r="C82" s="270" t="s">
         <v>72</v>
       </c>
       <c r="D82" s="137" t="s">
@@ -6920,14 +6920,14 @@
       <c r="Q82" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R82" s="254" t="s">
+      <c r="R82" s="257" t="s">
         <v>73</v>
       </c>
-      <c r="S82" s="255"/>
+      <c r="S82" s="258"/>
     </row>
     <row r="83" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="277"/>
-      <c r="C83" s="279"/>
+      <c r="B83" s="269"/>
+      <c r="C83" s="271"/>
       <c r="D83" s="137" t="s">
         <v>22</v>
       </c>
@@ -6973,8 +6973,8 @@
       <c r="Q83" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R83" s="256"/>
-      <c r="S83" s="257"/>
+      <c r="R83" s="259"/>
+      <c r="S83" s="260"/>
     </row>
     <row r="84" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B84" s="216" t="s">
@@ -6996,16 +6996,16 @@
       <c r="P84" s="217"/>
       <c r="Q84" s="217"/>
       <c r="R84" s="217"/>
-      <c r="S84" s="239"/>
+      <c r="S84" s="245"/>
     </row>
     <row r="85" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B85" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="240" t="s">
+      <c r="C85" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="241"/>
+      <c r="D85" s="274"/>
       <c r="E85" s="120" t="s">
         <v>3</v>
       </c>
@@ -7045,16 +7045,16 @@
       <c r="Q85" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R85" s="240" t="s">
+      <c r="R85" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S85" s="242"/>
+      <c r="S85" s="275"/>
     </row>
     <row r="86" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="243" t="s">
-        <v>75</v>
-      </c>
-      <c r="C86" s="244" t="s">
+      <c r="B86" s="248" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" s="249" t="s">
         <v>72</v>
       </c>
       <c r="D86" s="137" t="s">
@@ -7102,14 +7102,14 @@
       <c r="Q86" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R86" s="254" t="s">
+      <c r="R86" s="257" t="s">
         <v>73</v>
       </c>
-      <c r="S86" s="255"/>
+      <c r="S86" s="258"/>
     </row>
     <row r="87" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B87" s="243"/>
-      <c r="C87" s="244"/>
+      <c r="B87" s="248"/>
+      <c r="C87" s="249"/>
       <c r="D87" s="137" t="s">
         <v>22</v>
       </c>
@@ -7155,39 +7155,39 @@
       <c r="Q87" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R87" s="256"/>
-      <c r="S87" s="257"/>
+      <c r="R87" s="259"/>
+      <c r="S87" s="260"/>
     </row>
     <row r="88" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B88" s="250" t="s">
+      <c r="B88" s="276" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="251"/>
-      <c r="D88" s="251"/>
-      <c r="E88" s="251"/>
-      <c r="F88" s="251"/>
-      <c r="G88" s="251"/>
-      <c r="H88" s="251"/>
-      <c r="I88" s="251"/>
-      <c r="J88" s="251"/>
-      <c r="K88" s="251"/>
-      <c r="L88" s="251"/>
-      <c r="M88" s="251"/>
-      <c r="N88" s="251"/>
-      <c r="O88" s="251"/>
-      <c r="P88" s="251"/>
-      <c r="Q88" s="251"/>
-      <c r="R88" s="251"/>
-      <c r="S88" s="252"/>
+      <c r="C88" s="230"/>
+      <c r="D88" s="230"/>
+      <c r="E88" s="230"/>
+      <c r="F88" s="230"/>
+      <c r="G88" s="230"/>
+      <c r="H88" s="230"/>
+      <c r="I88" s="230"/>
+      <c r="J88" s="230"/>
+      <c r="K88" s="230"/>
+      <c r="L88" s="230"/>
+      <c r="M88" s="230"/>
+      <c r="N88" s="230"/>
+      <c r="O88" s="230"/>
+      <c r="P88" s="230"/>
+      <c r="Q88" s="230"/>
+      <c r="R88" s="230"/>
+      <c r="S88" s="277"/>
     </row>
     <row r="89" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B89" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="240" t="s">
+      <c r="C89" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="241"/>
+      <c r="D89" s="274"/>
       <c r="E89" s="120" t="s">
         <v>3</v>
       </c>
@@ -7227,16 +7227,16 @@
       <c r="Q89" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R89" s="240" t="s">
+      <c r="R89" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S89" s="242"/>
+      <c r="S89" s="275"/>
     </row>
     <row r="90" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="243" t="s">
+      <c r="B90" s="248" t="s">
         <v>78</v>
       </c>
-      <c r="C90" s="244" t="s">
+      <c r="C90" s="249" t="s">
         <v>72</v>
       </c>
       <c r="D90" s="137" t="s">
@@ -7284,14 +7284,14 @@
       <c r="Q90" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R90" s="254" t="s">
+      <c r="R90" s="257" t="s">
         <v>73</v>
       </c>
-      <c r="S90" s="255"/>
+      <c r="S90" s="258"/>
     </row>
     <row r="91" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="243"/>
-      <c r="C91" s="244"/>
+      <c r="B91" s="248"/>
+      <c r="C91" s="249"/>
       <c r="D91" s="137" t="s">
         <v>22</v>
       </c>
@@ -7337,39 +7337,39 @@
       <c r="Q91" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R91" s="256"/>
-      <c r="S91" s="257"/>
+      <c r="R91" s="259"/>
+      <c r="S91" s="260"/>
     </row>
     <row r="92" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B92" s="250" t="s">
+      <c r="B92" s="276" t="s">
         <v>79</v>
       </c>
-      <c r="C92" s="251"/>
-      <c r="D92" s="251"/>
-      <c r="E92" s="251"/>
-      <c r="F92" s="251"/>
-      <c r="G92" s="251"/>
-      <c r="H92" s="251"/>
-      <c r="I92" s="251"/>
-      <c r="J92" s="251"/>
-      <c r="K92" s="251"/>
-      <c r="L92" s="251"/>
-      <c r="M92" s="251"/>
-      <c r="N92" s="251"/>
-      <c r="O92" s="251"/>
-      <c r="P92" s="251"/>
-      <c r="Q92" s="251"/>
-      <c r="R92" s="251"/>
-      <c r="S92" s="252"/>
+      <c r="C92" s="230"/>
+      <c r="D92" s="230"/>
+      <c r="E92" s="230"/>
+      <c r="F92" s="230"/>
+      <c r="G92" s="230"/>
+      <c r="H92" s="230"/>
+      <c r="I92" s="230"/>
+      <c r="J92" s="230"/>
+      <c r="K92" s="230"/>
+      <c r="L92" s="230"/>
+      <c r="M92" s="230"/>
+      <c r="N92" s="230"/>
+      <c r="O92" s="230"/>
+      <c r="P92" s="230"/>
+      <c r="Q92" s="230"/>
+      <c r="R92" s="230"/>
+      <c r="S92" s="277"/>
     </row>
     <row r="93" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B93" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="240" t="s">
+      <c r="C93" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="241"/>
+      <c r="D93" s="274"/>
       <c r="E93" s="120" t="s">
         <v>3</v>
       </c>
@@ -7409,16 +7409,16 @@
       <c r="Q93" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R93" s="240" t="s">
+      <c r="R93" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S93" s="242"/>
+      <c r="S93" s="275"/>
     </row>
     <row r="94" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="243" t="s">
+      <c r="B94" s="248" t="s">
         <v>80</v>
       </c>
-      <c r="C94" s="244" t="s">
+      <c r="C94" s="249" t="s">
         <v>72</v>
       </c>
       <c r="D94" s="137" t="s">
@@ -7466,14 +7466,14 @@
       <c r="Q94" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R94" s="254" t="s">
+      <c r="R94" s="257" t="s">
         <v>73</v>
       </c>
-      <c r="S94" s="255"/>
+      <c r="S94" s="258"/>
     </row>
     <row r="95" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="243"/>
-      <c r="C95" s="244"/>
+      <c r="B95" s="248"/>
+      <c r="C95" s="249"/>
       <c r="D95" s="137" t="s">
         <v>22</v>
       </c>
@@ -7519,8 +7519,8 @@
       <c r="Q95" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R95" s="256"/>
-      <c r="S95" s="257"/>
+      <c r="R95" s="259"/>
+      <c r="S95" s="260"/>
     </row>
     <row r="96" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B96" s="216" t="s">
@@ -7541,17 +7541,17 @@
       <c r="O96" s="217"/>
       <c r="P96" s="217"/>
       <c r="Q96" s="217"/>
-      <c r="R96" s="249"/>
-      <c r="S96" s="249"/>
+      <c r="R96" s="223"/>
+      <c r="S96" s="223"/>
     </row>
     <row r="97" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B97" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="240" t="s">
+      <c r="C97" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="241"/>
+      <c r="D97" s="274"/>
       <c r="E97" s="120" t="s">
         <v>3</v>
       </c>
@@ -7591,16 +7591,16 @@
       <c r="Q97" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R97" s="240" t="s">
+      <c r="R97" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S97" s="242"/>
+      <c r="S97" s="275"/>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B98" s="243" t="s">
+      <c r="B98" s="248" t="s">
         <v>84</v>
       </c>
-      <c r="C98" s="244" t="s">
+      <c r="C98" s="249" t="s">
         <v>72</v>
       </c>
       <c r="D98" s="137" t="s">
@@ -7648,15 +7648,15 @@
       <c r="Q98" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R98" s="245" t="s">
-        <v>85</v>
-      </c>
-      <c r="S98" s="246"/>
+      <c r="R98" s="250" t="s">
+        <v>85</v>
+      </c>
+      <c r="S98" s="251"/>
       <c r="T98"/>
     </row>
     <row r="99" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="243"/>
-      <c r="C99" s="244"/>
+      <c r="B99" s="248"/>
+      <c r="C99" s="249"/>
       <c r="D99" s="137" t="s">
         <v>22</v>
       </c>
@@ -7702,8 +7702,8 @@
       <c r="Q99" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R99" s="247"/>
-      <c r="S99" s="248"/>
+      <c r="R99" s="252"/>
+      <c r="S99" s="253"/>
       <c r="T99"/>
     </row>
     <row r="100" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
@@ -7726,16 +7726,16 @@
       <c r="P100" s="217"/>
       <c r="Q100" s="217"/>
       <c r="R100" s="217"/>
-      <c r="S100" s="239"/>
+      <c r="S100" s="245"/>
     </row>
     <row r="101" spans="2:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B101" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="240" t="s">
+      <c r="C101" s="273" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="241"/>
+      <c r="D101" s="274"/>
       <c r="E101" s="120" t="s">
         <v>3</v>
       </c>
@@ -7775,16 +7775,16 @@
       <c r="Q101" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="R101" s="240" t="s">
+      <c r="R101" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="S101" s="242"/>
+      <c r="S101" s="275"/>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B102" s="243" t="s">
+      <c r="B102" s="248" t="s">
         <v>87</v>
       </c>
-      <c r="C102" s="244" t="s">
+      <c r="C102" s="249" t="s">
         <v>29</v>
       </c>
       <c r="D102" s="137" t="s">
@@ -7832,15 +7832,15 @@
       <c r="Q102" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R102" s="245" t="s">
-        <v>85</v>
-      </c>
-      <c r="S102" s="246"/>
+      <c r="R102" s="250" t="s">
+        <v>85</v>
+      </c>
+      <c r="S102" s="251"/>
       <c r="T102"/>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B103" s="243"/>
-      <c r="C103" s="244"/>
+      <c r="B103" s="248"/>
+      <c r="C103" s="249"/>
       <c r="D103" s="137" t="s">
         <v>22</v>
       </c>
@@ -7886,8 +7886,8 @@
       <c r="Q103" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="R103" s="247"/>
-      <c r="S103" s="248"/>
+      <c r="R103" s="252"/>
+      <c r="S103" s="253"/>
       <c r="T103"/>
     </row>
     <row r="104" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7911,127 +7911,127 @@
       <c r="S104" s="134"/>
     </row>
     <row r="105" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B105" s="227" t="s">
+      <c r="B105" s="278" t="s">
         <v>32</v>
       </c>
-      <c r="C105" s="228"/>
-      <c r="D105" s="228"/>
-      <c r="E105" s="228"/>
-      <c r="F105" s="228"/>
-      <c r="G105" s="228"/>
-      <c r="H105" s="228"/>
-      <c r="I105" s="228"/>
-      <c r="J105" s="228"/>
-      <c r="K105" s="228"/>
-      <c r="L105" s="228"/>
-      <c r="M105" s="228"/>
-      <c r="N105" s="228"/>
-      <c r="O105" s="228"/>
-      <c r="P105" s="228"/>
-      <c r="Q105" s="228"/>
-      <c r="R105" s="228"/>
-      <c r="S105" s="229"/>
+      <c r="C105" s="279"/>
+      <c r="D105" s="279"/>
+      <c r="E105" s="279"/>
+      <c r="F105" s="279"/>
+      <c r="G105" s="279"/>
+      <c r="H105" s="279"/>
+      <c r="I105" s="279"/>
+      <c r="J105" s="279"/>
+      <c r="K105" s="279"/>
+      <c r="L105" s="279"/>
+      <c r="M105" s="279"/>
+      <c r="N105" s="279"/>
+      <c r="O105" s="279"/>
+      <c r="P105" s="279"/>
+      <c r="Q105" s="279"/>
+      <c r="R105" s="279"/>
+      <c r="S105" s="280"/>
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B106" s="230" t="s">
+      <c r="B106" s="281" t="s">
         <v>33</v>
       </c>
-      <c r="C106" s="231"/>
-      <c r="D106" s="231"/>
-      <c r="E106" s="231"/>
-      <c r="F106" s="231"/>
-      <c r="G106" s="231"/>
-      <c r="H106" s="231"/>
-      <c r="I106" s="231"/>
-      <c r="J106" s="231"/>
-      <c r="K106" s="231"/>
-      <c r="L106" s="231"/>
-      <c r="M106" s="231"/>
-      <c r="N106" s="231"/>
-      <c r="O106" s="231"/>
-      <c r="P106" s="231"/>
-      <c r="Q106" s="231"/>
-      <c r="R106" s="231"/>
-      <c r="S106" s="232"/>
+      <c r="C106" s="282"/>
+      <c r="D106" s="282"/>
+      <c r="E106" s="282"/>
+      <c r="F106" s="282"/>
+      <c r="G106" s="282"/>
+      <c r="H106" s="282"/>
+      <c r="I106" s="282"/>
+      <c r="J106" s="282"/>
+      <c r="K106" s="282"/>
+      <c r="L106" s="282"/>
+      <c r="M106" s="282"/>
+      <c r="N106" s="282"/>
+      <c r="O106" s="282"/>
+      <c r="P106" s="282"/>
+      <c r="Q106" s="282"/>
+      <c r="R106" s="282"/>
+      <c r="S106" s="283"/>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B107" s="230"/>
-      <c r="C107" s="231"/>
-      <c r="D107" s="231"/>
-      <c r="E107" s="231"/>
-      <c r="F107" s="231"/>
-      <c r="G107" s="231"/>
-      <c r="H107" s="231"/>
-      <c r="I107" s="231"/>
-      <c r="J107" s="231"/>
-      <c r="K107" s="231"/>
-      <c r="L107" s="231"/>
-      <c r="M107" s="231"/>
-      <c r="N107" s="231"/>
-      <c r="O107" s="231"/>
-      <c r="P107" s="231"/>
-      <c r="Q107" s="231"/>
-      <c r="R107" s="231"/>
-      <c r="S107" s="232"/>
+      <c r="B107" s="281"/>
+      <c r="C107" s="282"/>
+      <c r="D107" s="282"/>
+      <c r="E107" s="282"/>
+      <c r="F107" s="282"/>
+      <c r="G107" s="282"/>
+      <c r="H107" s="282"/>
+      <c r="I107" s="282"/>
+      <c r="J107" s="282"/>
+      <c r="K107" s="282"/>
+      <c r="L107" s="282"/>
+      <c r="M107" s="282"/>
+      <c r="N107" s="282"/>
+      <c r="O107" s="282"/>
+      <c r="P107" s="282"/>
+      <c r="Q107" s="282"/>
+      <c r="R107" s="282"/>
+      <c r="S107" s="283"/>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B108" s="230"/>
-      <c r="C108" s="231"/>
-      <c r="D108" s="231"/>
-      <c r="E108" s="231"/>
-      <c r="F108" s="231"/>
-      <c r="G108" s="231"/>
-      <c r="H108" s="231"/>
-      <c r="I108" s="231"/>
-      <c r="J108" s="231"/>
-      <c r="K108" s="231"/>
-      <c r="L108" s="231"/>
-      <c r="M108" s="231"/>
-      <c r="N108" s="231"/>
-      <c r="O108" s="231"/>
-      <c r="P108" s="231"/>
-      <c r="Q108" s="231"/>
-      <c r="R108" s="231"/>
-      <c r="S108" s="232"/>
+      <c r="B108" s="281"/>
+      <c r="C108" s="282"/>
+      <c r="D108" s="282"/>
+      <c r="E108" s="282"/>
+      <c r="F108" s="282"/>
+      <c r="G108" s="282"/>
+      <c r="H108" s="282"/>
+      <c r="I108" s="282"/>
+      <c r="J108" s="282"/>
+      <c r="K108" s="282"/>
+      <c r="L108" s="282"/>
+      <c r="M108" s="282"/>
+      <c r="N108" s="282"/>
+      <c r="O108" s="282"/>
+      <c r="P108" s="282"/>
+      <c r="Q108" s="282"/>
+      <c r="R108" s="282"/>
+      <c r="S108" s="283"/>
     </row>
     <row r="109" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="233"/>
-      <c r="C109" s="234"/>
-      <c r="D109" s="234"/>
-      <c r="E109" s="234"/>
-      <c r="F109" s="234"/>
-      <c r="G109" s="234"/>
-      <c r="H109" s="234"/>
-      <c r="I109" s="234"/>
-      <c r="J109" s="234"/>
-      <c r="K109" s="234"/>
-      <c r="L109" s="234"/>
-      <c r="M109" s="234"/>
-      <c r="N109" s="234"/>
-      <c r="O109" s="234"/>
-      <c r="P109" s="234"/>
-      <c r="Q109" s="234"/>
-      <c r="R109" s="234"/>
-      <c r="S109" s="235"/>
+      <c r="B109" s="284"/>
+      <c r="C109" s="285"/>
+      <c r="D109" s="285"/>
+      <c r="E109" s="285"/>
+      <c r="F109" s="285"/>
+      <c r="G109" s="285"/>
+      <c r="H109" s="285"/>
+      <c r="I109" s="285"/>
+      <c r="J109" s="285"/>
+      <c r="K109" s="285"/>
+      <c r="L109" s="285"/>
+      <c r="M109" s="285"/>
+      <c r="N109" s="285"/>
+      <c r="O109" s="285"/>
+      <c r="P109" s="285"/>
+      <c r="Q109" s="285"/>
+      <c r="R109" s="285"/>
+      <c r="S109" s="286"/>
     </row>
     <row r="118" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B118" s="236" t="s">
+      <c r="B118" s="287" t="s">
         <v>88</v>
       </c>
-      <c r="C118" s="236"/>
-      <c r="D118" s="236"/>
-      <c r="E118" s="236"/>
-      <c r="F118" s="236"/>
-      <c r="G118" s="236"/>
-      <c r="H118" s="236"/>
-      <c r="I118" s="236"/>
-      <c r="J118" s="236"/>
-      <c r="K118" s="236"/>
-      <c r="L118" s="236"/>
-      <c r="M118" s="236"/>
-      <c r="N118" s="236"/>
-      <c r="O118" s="236"/>
-      <c r="P118" s="236"/>
+      <c r="C118" s="287"/>
+      <c r="D118" s="287"/>
+      <c r="E118" s="287"/>
+      <c r="F118" s="287"/>
+      <c r="G118" s="287"/>
+      <c r="H118" s="287"/>
+      <c r="I118" s="287"/>
+      <c r="J118" s="287"/>
+      <c r="K118" s="287"/>
+      <c r="L118" s="287"/>
+      <c r="M118" s="287"/>
+      <c r="N118" s="287"/>
+      <c r="O118" s="287"/>
+      <c r="P118" s="287"/>
       <c r="Q118" s="129"/>
     </row>
     <row r="119" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -8082,7 +8082,7 @@
       <c r="B120" s="220" t="s">
         <v>90</v>
       </c>
-      <c r="C120" s="237" t="s">
+      <c r="C120" s="228" t="s">
         <v>16</v>
       </c>
       <c r="D120" s="20" t="s">
@@ -8120,15 +8120,15 @@
       <c r="N120" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O120" s="238" t="s">
+      <c r="O120" s="236" t="s">
         <v>44</v>
       </c>
-      <c r="P120" s="238"/>
-      <c r="Q120" s="238"/>
+      <c r="P120" s="236"/>
+      <c r="Q120" s="236"/>
     </row>
     <row r="121" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B121" s="220"/>
-      <c r="C121" s="237"/>
+      <c r="C121" s="228"/>
       <c r="D121" s="20" t="s">
         <v>22</v>
       </c>
@@ -8164,9 +8164,9 @@
       <c r="N121" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O121" s="238"/>
-      <c r="P121" s="238"/>
-      <c r="Q121" s="238"/>
+      <c r="O121" s="236"/>
+      <c r="P121" s="236"/>
+      <c r="Q121" s="236"/>
     </row>
     <row r="122" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B122" s="42"/>
@@ -8207,78 +8207,78 @@
       <c r="Q123" s="7"/>
     </row>
     <row r="124" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B124" s="221" t="s">
+      <c r="B124" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="C124" s="222"/>
-      <c r="D124" s="222"/>
-      <c r="E124" s="222"/>
-      <c r="F124" s="222"/>
-      <c r="G124" s="222"/>
-      <c r="H124" s="222"/>
-      <c r="I124" s="222"/>
-      <c r="J124" s="222"/>
-      <c r="K124" s="222"/>
-      <c r="L124" s="222"/>
-      <c r="M124" s="222"/>
-      <c r="N124" s="222"/>
-      <c r="O124" s="222"/>
-      <c r="P124" s="222"/>
-      <c r="Q124" s="223"/>
+      <c r="C124" s="240"/>
+      <c r="D124" s="240"/>
+      <c r="E124" s="240"/>
+      <c r="F124" s="240"/>
+      <c r="G124" s="240"/>
+      <c r="H124" s="240"/>
+      <c r="I124" s="240"/>
+      <c r="J124" s="240"/>
+      <c r="K124" s="240"/>
+      <c r="L124" s="240"/>
+      <c r="M124" s="240"/>
+      <c r="N124" s="240"/>
+      <c r="O124" s="240"/>
+      <c r="P124" s="240"/>
+      <c r="Q124" s="241"/>
     </row>
     <row r="125" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B125" s="221"/>
-      <c r="C125" s="222"/>
-      <c r="D125" s="222"/>
-      <c r="E125" s="222"/>
-      <c r="F125" s="222"/>
-      <c r="G125" s="222"/>
-      <c r="H125" s="222"/>
-      <c r="I125" s="222"/>
-      <c r="J125" s="222"/>
-      <c r="K125" s="222"/>
-      <c r="L125" s="222"/>
-      <c r="M125" s="222"/>
-      <c r="N125" s="222"/>
-      <c r="O125" s="222"/>
-      <c r="P125" s="222"/>
-      <c r="Q125" s="223"/>
+      <c r="B125" s="239"/>
+      <c r="C125" s="240"/>
+      <c r="D125" s="240"/>
+      <c r="E125" s="240"/>
+      <c r="F125" s="240"/>
+      <c r="G125" s="240"/>
+      <c r="H125" s="240"/>
+      <c r="I125" s="240"/>
+      <c r="J125" s="240"/>
+      <c r="K125" s="240"/>
+      <c r="L125" s="240"/>
+      <c r="M125" s="240"/>
+      <c r="N125" s="240"/>
+      <c r="O125" s="240"/>
+      <c r="P125" s="240"/>
+      <c r="Q125" s="241"/>
     </row>
     <row r="126" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B126" s="221"/>
-      <c r="C126" s="222"/>
-      <c r="D126" s="222"/>
-      <c r="E126" s="222"/>
-      <c r="F126" s="222"/>
-      <c r="G126" s="222"/>
-      <c r="H126" s="222"/>
-      <c r="I126" s="222"/>
-      <c r="J126" s="222"/>
-      <c r="K126" s="222"/>
-      <c r="L126" s="222"/>
-      <c r="M126" s="222"/>
-      <c r="N126" s="222"/>
-      <c r="O126" s="222"/>
-      <c r="P126" s="222"/>
-      <c r="Q126" s="223"/>
+      <c r="B126" s="239"/>
+      <c r="C126" s="240"/>
+      <c r="D126" s="240"/>
+      <c r="E126" s="240"/>
+      <c r="F126" s="240"/>
+      <c r="G126" s="240"/>
+      <c r="H126" s="240"/>
+      <c r="I126" s="240"/>
+      <c r="J126" s="240"/>
+      <c r="K126" s="240"/>
+      <c r="L126" s="240"/>
+      <c r="M126" s="240"/>
+      <c r="N126" s="240"/>
+      <c r="O126" s="240"/>
+      <c r="P126" s="240"/>
+      <c r="Q126" s="241"/>
     </row>
     <row r="127" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B127" s="224"/>
-      <c r="C127" s="225"/>
-      <c r="D127" s="225"/>
-      <c r="E127" s="225"/>
-      <c r="F127" s="225"/>
-      <c r="G127" s="225"/>
-      <c r="H127" s="225"/>
-      <c r="I127" s="225"/>
-      <c r="J127" s="225"/>
-      <c r="K127" s="225"/>
-      <c r="L127" s="225"/>
-      <c r="M127" s="225"/>
-      <c r="N127" s="225"/>
-      <c r="O127" s="225"/>
-      <c r="P127" s="225"/>
-      <c r="Q127" s="226"/>
+      <c r="B127" s="242"/>
+      <c r="C127" s="243"/>
+      <c r="D127" s="243"/>
+      <c r="E127" s="243"/>
+      <c r="F127" s="243"/>
+      <c r="G127" s="243"/>
+      <c r="H127" s="243"/>
+      <c r="I127" s="243"/>
+      <c r="J127" s="243"/>
+      <c r="K127" s="243"/>
+      <c r="L127" s="243"/>
+      <c r="M127" s="243"/>
+      <c r="N127" s="243"/>
+      <c r="O127" s="243"/>
+      <c r="P127" s="243"/>
+      <c r="Q127" s="244"/>
     </row>
     <row r="128" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B128" s="35"/>
@@ -8616,7 +8616,7 @@
         <v>100</v>
       </c>
       <c r="O143" s="208" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="P143" s="94" t="s">
         <v>91</v>
@@ -8661,7 +8661,7 @@
         <v>100</v>
       </c>
       <c r="O144" s="208" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="P144" s="94" t="s">
         <v>91</v>
@@ -8678,7 +8678,7 @@
         <v>17</v>
       </c>
       <c r="E145" s="95">
-        <v>950</v>
+        <v>1050</v>
       </c>
       <c r="F145" s="95">
         <v>289</v>
@@ -8697,20 +8697,20 @@
       </c>
       <c r="K145" s="96">
         <f>SUM(E145:J145)</f>
-        <v>1528.38</v>
+        <v>1628.38</v>
       </c>
       <c r="L145" s="95">
         <v>200</v>
       </c>
       <c r="M145" s="96">
         <f>SUM(K145:L145)</f>
-        <v>1728.38</v>
+        <v>1828.38</v>
       </c>
       <c r="N145" s="94" t="s">
         <v>100</v>
       </c>
       <c r="O145" s="208" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="P145" s="94" t="s">
         <v>58</v>
@@ -8723,7 +8723,7 @@
         <v>22</v>
       </c>
       <c r="E146" s="95">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="F146" s="95">
         <v>289</v>
@@ -8742,20 +8742,20 @@
       </c>
       <c r="K146" s="96">
         <f>SUM(E146:J146)</f>
-        <v>1928.38</v>
+        <v>2078.38</v>
       </c>
       <c r="L146" s="95">
         <v>200</v>
       </c>
       <c r="M146" s="96">
         <f>SUM(K146:L146)</f>
-        <v>2128.38</v>
+        <v>2278.38</v>
       </c>
       <c r="N146" s="94" t="s">
         <v>100</v>
       </c>
       <c r="O146" s="208" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="P146" s="94" t="s">
         <v>58</v>
@@ -8788,78 +8788,78 @@
       <c r="Q148" s="7"/>
     </row>
     <row r="149" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B149" s="221" t="s">
+      <c r="B149" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="C149" s="222"/>
-      <c r="D149" s="222"/>
-      <c r="E149" s="222"/>
-      <c r="F149" s="222"/>
-      <c r="G149" s="222"/>
-      <c r="H149" s="222"/>
-      <c r="I149" s="222"/>
-      <c r="J149" s="222"/>
-      <c r="K149" s="222"/>
-      <c r="L149" s="222"/>
-      <c r="M149" s="222"/>
-      <c r="N149" s="222"/>
-      <c r="O149" s="222"/>
-      <c r="P149" s="222"/>
-      <c r="Q149" s="223"/>
+      <c r="C149" s="240"/>
+      <c r="D149" s="240"/>
+      <c r="E149" s="240"/>
+      <c r="F149" s="240"/>
+      <c r="G149" s="240"/>
+      <c r="H149" s="240"/>
+      <c r="I149" s="240"/>
+      <c r="J149" s="240"/>
+      <c r="K149" s="240"/>
+      <c r="L149" s="240"/>
+      <c r="M149" s="240"/>
+      <c r="N149" s="240"/>
+      <c r="O149" s="240"/>
+      <c r="P149" s="240"/>
+      <c r="Q149" s="241"/>
     </row>
     <row r="150" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B150" s="221"/>
-      <c r="C150" s="222"/>
-      <c r="D150" s="222"/>
-      <c r="E150" s="222"/>
-      <c r="F150" s="222"/>
-      <c r="G150" s="222"/>
-      <c r="H150" s="222"/>
-      <c r="I150" s="222"/>
-      <c r="J150" s="222"/>
-      <c r="K150" s="222"/>
-      <c r="L150" s="222"/>
-      <c r="M150" s="222"/>
-      <c r="N150" s="222"/>
-      <c r="O150" s="222"/>
-      <c r="P150" s="222"/>
-      <c r="Q150" s="223"/>
+      <c r="B150" s="239"/>
+      <c r="C150" s="240"/>
+      <c r="D150" s="240"/>
+      <c r="E150" s="240"/>
+      <c r="F150" s="240"/>
+      <c r="G150" s="240"/>
+      <c r="H150" s="240"/>
+      <c r="I150" s="240"/>
+      <c r="J150" s="240"/>
+      <c r="K150" s="240"/>
+      <c r="L150" s="240"/>
+      <c r="M150" s="240"/>
+      <c r="N150" s="240"/>
+      <c r="O150" s="240"/>
+      <c r="P150" s="240"/>
+      <c r="Q150" s="241"/>
     </row>
     <row r="151" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B151" s="221"/>
-      <c r="C151" s="222"/>
-      <c r="D151" s="222"/>
-      <c r="E151" s="222"/>
-      <c r="F151" s="222"/>
-      <c r="G151" s="222"/>
-      <c r="H151" s="222"/>
-      <c r="I151" s="222"/>
-      <c r="J151" s="222"/>
-      <c r="K151" s="222"/>
-      <c r="L151" s="222"/>
-      <c r="M151" s="222"/>
-      <c r="N151" s="222"/>
-      <c r="O151" s="222"/>
-      <c r="P151" s="222"/>
-      <c r="Q151" s="223"/>
+      <c r="B151" s="239"/>
+      <c r="C151" s="240"/>
+      <c r="D151" s="240"/>
+      <c r="E151" s="240"/>
+      <c r="F151" s="240"/>
+      <c r="G151" s="240"/>
+      <c r="H151" s="240"/>
+      <c r="I151" s="240"/>
+      <c r="J151" s="240"/>
+      <c r="K151" s="240"/>
+      <c r="L151" s="240"/>
+      <c r="M151" s="240"/>
+      <c r="N151" s="240"/>
+      <c r="O151" s="240"/>
+      <c r="P151" s="240"/>
+      <c r="Q151" s="241"/>
     </row>
     <row r="152" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B152" s="224"/>
-      <c r="C152" s="225"/>
-      <c r="D152" s="225"/>
-      <c r="E152" s="225"/>
-      <c r="F152" s="225"/>
-      <c r="G152" s="225"/>
-      <c r="H152" s="225"/>
-      <c r="I152" s="225"/>
-      <c r="J152" s="225"/>
-      <c r="K152" s="225"/>
-      <c r="L152" s="225"/>
-      <c r="M152" s="225"/>
-      <c r="N152" s="225"/>
-      <c r="O152" s="225"/>
-      <c r="P152" s="225"/>
-      <c r="Q152" s="226"/>
+      <c r="B152" s="242"/>
+      <c r="C152" s="243"/>
+      <c r="D152" s="243"/>
+      <c r="E152" s="243"/>
+      <c r="F152" s="243"/>
+      <c r="G152" s="243"/>
+      <c r="H152" s="243"/>
+      <c r="I152" s="243"/>
+      <c r="J152" s="243"/>
+      <c r="K152" s="243"/>
+      <c r="L152" s="243"/>
+      <c r="M152" s="243"/>
+      <c r="N152" s="243"/>
+      <c r="O152" s="243"/>
+      <c r="P152" s="243"/>
+      <c r="Q152" s="244"/>
     </row>
     <row r="154" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B154" s="35"/>
@@ -8954,7 +8954,7 @@
         <v>17</v>
       </c>
       <c r="E162" s="118">
-        <v>1950</v>
+        <v>1550</v>
       </c>
       <c r="F162" s="95">
         <v>340</v>
@@ -8973,20 +8973,20 @@
       </c>
       <c r="K162" s="96">
         <f>SUM(E162:J162)</f>
-        <v>2538</v>
+        <v>2138</v>
       </c>
       <c r="L162" s="95">
         <v>200</v>
       </c>
       <c r="M162" s="96">
         <f>SUM(K162:L162)</f>
-        <v>2738</v>
+        <v>2338</v>
       </c>
       <c r="N162" s="94" t="s">
         <v>95</v>
       </c>
       <c r="O162" s="208" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="P162" s="94" t="s">
         <v>82</v>
@@ -8999,7 +8999,7 @@
         <v>22</v>
       </c>
       <c r="E163" s="118">
-        <v>2250</v>
+        <v>2700</v>
       </c>
       <c r="F163" s="95">
         <v>340</v>
@@ -9018,20 +9018,20 @@
       </c>
       <c r="K163" s="96">
         <f>SUM(E163:J163)</f>
-        <v>2838</v>
+        <v>3288</v>
       </c>
       <c r="L163" s="95">
         <v>200</v>
       </c>
       <c r="M163" s="96">
         <f>SUM(K163:L163)</f>
-        <v>3038</v>
+        <v>3488</v>
       </c>
       <c r="N163" s="94" t="s">
         <v>95</v>
       </c>
       <c r="O163" s="208" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="P163" s="94" t="s">
         <v>82</v>
@@ -9058,78 +9058,78 @@
       <c r="Q165" s="7"/>
     </row>
     <row r="166" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B166" s="221" t="s">
+      <c r="B166" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="C166" s="222"/>
-      <c r="D166" s="222"/>
-      <c r="E166" s="222"/>
-      <c r="F166" s="222"/>
-      <c r="G166" s="222"/>
-      <c r="H166" s="222"/>
-      <c r="I166" s="222"/>
-      <c r="J166" s="222"/>
-      <c r="K166" s="222"/>
-      <c r="L166" s="222"/>
-      <c r="M166" s="222"/>
-      <c r="N166" s="222"/>
-      <c r="O166" s="222"/>
-      <c r="P166" s="222"/>
-      <c r="Q166" s="223"/>
+      <c r="C166" s="240"/>
+      <c r="D166" s="240"/>
+      <c r="E166" s="240"/>
+      <c r="F166" s="240"/>
+      <c r="G166" s="240"/>
+      <c r="H166" s="240"/>
+      <c r="I166" s="240"/>
+      <c r="J166" s="240"/>
+      <c r="K166" s="240"/>
+      <c r="L166" s="240"/>
+      <c r="M166" s="240"/>
+      <c r="N166" s="240"/>
+      <c r="O166" s="240"/>
+      <c r="P166" s="240"/>
+      <c r="Q166" s="241"/>
     </row>
     <row r="167" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B167" s="221"/>
-      <c r="C167" s="222"/>
-      <c r="D167" s="222"/>
-      <c r="E167" s="222"/>
-      <c r="F167" s="222"/>
-      <c r="G167" s="222"/>
-      <c r="H167" s="222"/>
-      <c r="I167" s="222"/>
-      <c r="J167" s="222"/>
-      <c r="K167" s="222"/>
-      <c r="L167" s="222"/>
-      <c r="M167" s="222"/>
-      <c r="N167" s="222"/>
-      <c r="O167" s="222"/>
-      <c r="P167" s="222"/>
-      <c r="Q167" s="223"/>
+      <c r="B167" s="239"/>
+      <c r="C167" s="240"/>
+      <c r="D167" s="240"/>
+      <c r="E167" s="240"/>
+      <c r="F167" s="240"/>
+      <c r="G167" s="240"/>
+      <c r="H167" s="240"/>
+      <c r="I167" s="240"/>
+      <c r="J167" s="240"/>
+      <c r="K167" s="240"/>
+      <c r="L167" s="240"/>
+      <c r="M167" s="240"/>
+      <c r="N167" s="240"/>
+      <c r="O167" s="240"/>
+      <c r="P167" s="240"/>
+      <c r="Q167" s="241"/>
     </row>
     <row r="168" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B168" s="221"/>
-      <c r="C168" s="222"/>
-      <c r="D168" s="222"/>
-      <c r="E168" s="222"/>
-      <c r="F168" s="222"/>
-      <c r="G168" s="222"/>
-      <c r="H168" s="222"/>
-      <c r="I168" s="222"/>
-      <c r="J168" s="222"/>
-      <c r="K168" s="222"/>
-      <c r="L168" s="222"/>
-      <c r="M168" s="222"/>
-      <c r="N168" s="222"/>
-      <c r="O168" s="222"/>
-      <c r="P168" s="222"/>
-      <c r="Q168" s="223"/>
+      <c r="B168" s="239"/>
+      <c r="C168" s="240"/>
+      <c r="D168" s="240"/>
+      <c r="E168" s="240"/>
+      <c r="F168" s="240"/>
+      <c r="G168" s="240"/>
+      <c r="H168" s="240"/>
+      <c r="I168" s="240"/>
+      <c r="J168" s="240"/>
+      <c r="K168" s="240"/>
+      <c r="L168" s="240"/>
+      <c r="M168" s="240"/>
+      <c r="N168" s="240"/>
+      <c r="O168" s="240"/>
+      <c r="P168" s="240"/>
+      <c r="Q168" s="241"/>
     </row>
     <row r="169" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B169" s="224"/>
-      <c r="C169" s="225"/>
-      <c r="D169" s="225"/>
-      <c r="E169" s="225"/>
-      <c r="F169" s="225"/>
-      <c r="G169" s="225"/>
-      <c r="H169" s="225"/>
-      <c r="I169" s="225"/>
-      <c r="J169" s="225"/>
-      <c r="K169" s="225"/>
-      <c r="L169" s="225"/>
-      <c r="M169" s="225"/>
-      <c r="N169" s="225"/>
-      <c r="O169" s="225"/>
-      <c r="P169" s="225"/>
-      <c r="Q169" s="226"/>
+      <c r="B169" s="242"/>
+      <c r="C169" s="243"/>
+      <c r="D169" s="243"/>
+      <c r="E169" s="243"/>
+      <c r="F169" s="243"/>
+      <c r="G169" s="243"/>
+      <c r="H169" s="243"/>
+      <c r="I169" s="243"/>
+      <c r="J169" s="243"/>
+      <c r="K169" s="243"/>
+      <c r="L169" s="243"/>
+      <c r="M169" s="243"/>
+      <c r="N169" s="243"/>
+      <c r="O169" s="243"/>
+      <c r="P169" s="243"/>
+      <c r="Q169" s="244"/>
     </row>
     <row r="170" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B170" s="35"/>
@@ -9168,24 +9168,24 @@
       <c r="Q171" s="35"/>
     </row>
     <row r="173" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B173" s="261" t="s">
+      <c r="B173" s="256" t="s">
         <v>106</v>
       </c>
-      <c r="C173" s="249"/>
-      <c r="D173" s="249"/>
-      <c r="E173" s="249"/>
-      <c r="F173" s="249"/>
-      <c r="G173" s="249"/>
-      <c r="H173" s="249"/>
-      <c r="I173" s="249"/>
-      <c r="J173" s="249"/>
-      <c r="K173" s="249"/>
-      <c r="L173" s="249"/>
-      <c r="M173" s="249"/>
-      <c r="N173" s="249"/>
-      <c r="O173" s="249"/>
-      <c r="P173" s="249"/>
-      <c r="Q173" s="249"/>
+      <c r="C173" s="223"/>
+      <c r="D173" s="223"/>
+      <c r="E173" s="223"/>
+      <c r="F173" s="223"/>
+      <c r="G173" s="223"/>
+      <c r="H173" s="223"/>
+      <c r="I173" s="223"/>
+      <c r="J173" s="223"/>
+      <c r="K173" s="223"/>
+      <c r="L173" s="223"/>
+      <c r="M173" s="223"/>
+      <c r="N173" s="223"/>
+      <c r="O173" s="223"/>
+      <c r="P173" s="223"/>
+      <c r="Q173" s="223"/>
     </row>
     <row r="174" spans="2:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B174" s="97" t="s">
@@ -9236,7 +9236,7 @@
       </c>
     </row>
     <row r="175" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B175" s="253" t="s">
+      <c r="B175" s="221" t="s">
         <v>112</v>
       </c>
       <c r="C175" s="220" t="s">
@@ -9288,7 +9288,7 @@
       </c>
     </row>
     <row r="176" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B176" s="270"/>
+      <c r="B176" s="222"/>
       <c r="C176" s="220"/>
       <c r="D176" s="117" t="s">
         <v>22</v>
@@ -9516,6 +9516,104 @@
     </row>
   </sheetData>
   <mergeCells count="122">
+    <mergeCell ref="B160:P160"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="B166:Q169"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="C145:C146"/>
+    <mergeCell ref="B149:Q152"/>
+    <mergeCell ref="B124:Q127"/>
+    <mergeCell ref="B134:P134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B141:P141"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="B105:S105"/>
+    <mergeCell ref="B106:S109"/>
+    <mergeCell ref="B118:P118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="O119:Q119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="O120:Q121"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="R102:S103"/>
+    <mergeCell ref="B96:S96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="R97:S97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="R98:S99"/>
+    <mergeCell ref="B92:S92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="R93:S93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="B100:S100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="R101:S101"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="R90:S91"/>
+    <mergeCell ref="B84:S84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="R85:S85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="R86:S87"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="R74:S79"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="B88:S88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="B173:Q173"/>
+    <mergeCell ref="R72:S73"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="R64:S65"/>
+    <mergeCell ref="R62:S63"/>
+    <mergeCell ref="R66:S67"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="R68:S71"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="R82:S83"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B80:S80"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B24:P27"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="B43:Q46"/>
+    <mergeCell ref="B56:S56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="R58:S61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
     <mergeCell ref="B186:P186"/>
     <mergeCell ref="C187:D187"/>
     <mergeCell ref="B188:B189"/>
@@ -9540,104 +9638,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B24:P27"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="B43:Q46"/>
-    <mergeCell ref="B56:S56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="R58:S61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B173:Q173"/>
-    <mergeCell ref="R72:S73"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="R64:S65"/>
-    <mergeCell ref="R62:S63"/>
-    <mergeCell ref="R66:S67"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="R68:S71"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="R82:S83"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="B80:S80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="R74:S79"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="B88:S88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="R90:S91"/>
-    <mergeCell ref="B84:S84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="R85:S85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="R86:S87"/>
-    <mergeCell ref="B92:S92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="R93:S93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="R94:S95"/>
-    <mergeCell ref="B100:S100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="R101:S101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="R102:S103"/>
-    <mergeCell ref="B96:S96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="R97:S97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="R98:S99"/>
-    <mergeCell ref="B124:Q127"/>
-    <mergeCell ref="B134:P134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="B141:P141"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="B105:S105"/>
-    <mergeCell ref="B106:S109"/>
-    <mergeCell ref="B118:P118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="O119:Q119"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="O120:Q121"/>
-    <mergeCell ref="B160:P160"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="B166:Q169"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="C145:C146"/>
-    <mergeCell ref="B149:Q152"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9674,33 +9674,33 @@
   </cols>
   <sheetData>
     <row r="9" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="249" t="s">
+      <c r="B9" s="223" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="249"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
-      <c r="M9" s="249"/>
-      <c r="N9" s="249"/>
-      <c r="O9" s="249"/>
-      <c r="P9" s="249"/>
-      <c r="Q9" s="249"/>
+      <c r="C9" s="223"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="223"/>
+      <c r="H9" s="223"/>
+      <c r="I9" s="223"/>
+      <c r="J9" s="223"/>
+      <c r="K9" s="223"/>
+      <c r="L9" s="223"/>
+      <c r="M9" s="223"/>
+      <c r="N9" s="223"/>
+      <c r="O9" s="223"/>
+      <c r="P9" s="223"/>
+      <c r="Q9" s="223"/>
     </row>
     <row r="10" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="302" t="s">
+      <c r="C10" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="302"/>
+      <c r="D10" s="303"/>
       <c r="E10" s="8" t="s">
         <v>3</v>
       </c>
@@ -9742,10 +9742,10 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="237" t="s">
+      <c r="B11" s="228" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="237" t="s">
+      <c r="C11" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D11" s="53" t="s">
@@ -9795,8 +9795,8 @@
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="237"/>
-      <c r="C12" s="237"/>
+      <c r="B12" s="228"/>
+      <c r="C12" s="228"/>
       <c r="D12" s="53" t="s">
         <v>22</v>
       </c>
@@ -9844,10 +9844,10 @@
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="228" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="237" t="s">
+      <c r="C13" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D13" s="53" t="s">
@@ -9897,8 +9897,8 @@
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="237"/>
-      <c r="C14" s="237"/>
+      <c r="B14" s="228"/>
+      <c r="C14" s="228"/>
       <c r="D14" s="53" t="s">
         <v>22</v>
       </c>
@@ -9946,10 +9946,10 @@
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="285" t="s">
+      <c r="B15" s="226" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="237" t="s">
+      <c r="C15" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D15" s="53" t="s">
@@ -9999,8 +9999,8 @@
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="285"/>
-      <c r="C16" s="237"/>
+      <c r="B16" s="226"/>
+      <c r="C16" s="228"/>
       <c r="D16" s="53" t="s">
         <v>22</v>
       </c>
@@ -10048,10 +10048,10 @@
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="228" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="237" t="s">
+      <c r="C17" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D17" s="53" t="s">
@@ -10101,8 +10101,8 @@
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="237"/>
-      <c r="C18" s="237"/>
+      <c r="B18" s="228"/>
+      <c r="C18" s="228"/>
       <c r="D18" s="53" t="s">
         <v>22</v>
       </c>
@@ -10167,103 +10167,103 @@
       <c r="Q19" s="34"/>
     </row>
     <row r="20" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="291" t="s">
+      <c r="B20" s="306" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="292"/>
-      <c r="D20" s="292"/>
-      <c r="E20" s="292"/>
-      <c r="F20" s="292"/>
-      <c r="G20" s="292"/>
-      <c r="H20" s="292"/>
-      <c r="I20" s="292"/>
-      <c r="J20" s="292"/>
-      <c r="K20" s="292"/>
-      <c r="L20" s="292"/>
-      <c r="M20" s="292"/>
-      <c r="N20" s="292"/>
-      <c r="O20" s="292"/>
-      <c r="P20" s="292"/>
-      <c r="Q20" s="292"/>
-      <c r="R20" s="293"/>
+      <c r="C20" s="307"/>
+      <c r="D20" s="307"/>
+      <c r="E20" s="307"/>
+      <c r="F20" s="307"/>
+      <c r="G20" s="307"/>
+      <c r="H20" s="307"/>
+      <c r="I20" s="307"/>
+      <c r="J20" s="307"/>
+      <c r="K20" s="307"/>
+      <c r="L20" s="307"/>
+      <c r="M20" s="307"/>
+      <c r="N20" s="307"/>
+      <c r="O20" s="307"/>
+      <c r="P20" s="307"/>
+      <c r="Q20" s="307"/>
+      <c r="R20" s="308"/>
     </row>
     <row r="21" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="294" t="s">
+      <c r="B21" s="309" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="295"/>
-      <c r="D21" s="295"/>
-      <c r="E21" s="295"/>
-      <c r="F21" s="295"/>
-      <c r="G21" s="295"/>
-      <c r="H21" s="295"/>
-      <c r="I21" s="295"/>
-      <c r="J21" s="295"/>
-      <c r="K21" s="295"/>
-      <c r="L21" s="295"/>
-      <c r="M21" s="295"/>
-      <c r="N21" s="295"/>
-      <c r="O21" s="295"/>
-      <c r="P21" s="295"/>
-      <c r="Q21" s="295"/>
-      <c r="R21" s="296"/>
+      <c r="C21" s="310"/>
+      <c r="D21" s="310"/>
+      <c r="E21" s="310"/>
+      <c r="F21" s="310"/>
+      <c r="G21" s="310"/>
+      <c r="H21" s="310"/>
+      <c r="I21" s="310"/>
+      <c r="J21" s="310"/>
+      <c r="K21" s="310"/>
+      <c r="L21" s="310"/>
+      <c r="M21" s="310"/>
+      <c r="N21" s="310"/>
+      <c r="O21" s="310"/>
+      <c r="P21" s="310"/>
+      <c r="Q21" s="310"/>
+      <c r="R21" s="311"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="297"/>
-      <c r="C22" s="231"/>
-      <c r="D22" s="231"/>
-      <c r="E22" s="231"/>
-      <c r="F22" s="231"/>
-      <c r="G22" s="231"/>
-      <c r="H22" s="231"/>
-      <c r="I22" s="231"/>
-      <c r="J22" s="231"/>
-      <c r="K22" s="231"/>
-      <c r="L22" s="231"/>
-      <c r="M22" s="231"/>
-      <c r="N22" s="231"/>
-      <c r="O22" s="231"/>
-      <c r="P22" s="231"/>
-      <c r="Q22" s="231"/>
-      <c r="R22" s="298"/>
+      <c r="B22" s="312"/>
+      <c r="C22" s="282"/>
+      <c r="D22" s="282"/>
+      <c r="E22" s="282"/>
+      <c r="F22" s="282"/>
+      <c r="G22" s="282"/>
+      <c r="H22" s="282"/>
+      <c r="I22" s="282"/>
+      <c r="J22" s="282"/>
+      <c r="K22" s="282"/>
+      <c r="L22" s="282"/>
+      <c r="M22" s="282"/>
+      <c r="N22" s="282"/>
+      <c r="O22" s="282"/>
+      <c r="P22" s="282"/>
+      <c r="Q22" s="282"/>
+      <c r="R22" s="313"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="297"/>
-      <c r="C23" s="231"/>
-      <c r="D23" s="231"/>
-      <c r="E23" s="231"/>
-      <c r="F23" s="231"/>
-      <c r="G23" s="231"/>
-      <c r="H23" s="231"/>
-      <c r="I23" s="231"/>
-      <c r="J23" s="231"/>
-      <c r="K23" s="231"/>
-      <c r="L23" s="231"/>
-      <c r="M23" s="231"/>
-      <c r="N23" s="231"/>
-      <c r="O23" s="231"/>
-      <c r="P23" s="231"/>
-      <c r="Q23" s="231"/>
-      <c r="R23" s="298"/>
+      <c r="B23" s="312"/>
+      <c r="C23" s="282"/>
+      <c r="D23" s="282"/>
+      <c r="E23" s="282"/>
+      <c r="F23" s="282"/>
+      <c r="G23" s="282"/>
+      <c r="H23" s="282"/>
+      <c r="I23" s="282"/>
+      <c r="J23" s="282"/>
+      <c r="K23" s="282"/>
+      <c r="L23" s="282"/>
+      <c r="M23" s="282"/>
+      <c r="N23" s="282"/>
+      <c r="O23" s="282"/>
+      <c r="P23" s="282"/>
+      <c r="Q23" s="282"/>
+      <c r="R23" s="313"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B24" s="299"/>
-      <c r="C24" s="300"/>
-      <c r="D24" s="300"/>
-      <c r="E24" s="300"/>
-      <c r="F24" s="300"/>
-      <c r="G24" s="300"/>
-      <c r="H24" s="300"/>
-      <c r="I24" s="300"/>
-      <c r="J24" s="300"/>
-      <c r="K24" s="300"/>
-      <c r="L24" s="300"/>
-      <c r="M24" s="300"/>
-      <c r="N24" s="300"/>
-      <c r="O24" s="300"/>
-      <c r="P24" s="300"/>
-      <c r="Q24" s="300"/>
-      <c r="R24" s="301"/>
+      <c r="B24" s="314"/>
+      <c r="C24" s="315"/>
+      <c r="D24" s="315"/>
+      <c r="E24" s="315"/>
+      <c r="F24" s="315"/>
+      <c r="G24" s="315"/>
+      <c r="H24" s="315"/>
+      <c r="I24" s="315"/>
+      <c r="J24" s="315"/>
+      <c r="K24" s="315"/>
+      <c r="L24" s="315"/>
+      <c r="M24" s="315"/>
+      <c r="N24" s="315"/>
+      <c r="O24" s="315"/>
+      <c r="P24" s="315"/>
+      <c r="Q24" s="315"/>
+      <c r="R24" s="316"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="27"/>
@@ -10419,34 +10419,34 @@
       <c r="Q33" s="34"/>
     </row>
     <row r="34" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="287" t="s">
+      <c r="B34" s="229" t="s">
         <v>127</v>
       </c>
-      <c r="C34" s="287"/>
-      <c r="D34" s="287"/>
-      <c r="E34" s="287"/>
-      <c r="F34" s="287"/>
-      <c r="G34" s="287"/>
-      <c r="H34" s="287"/>
-      <c r="I34" s="287"/>
-      <c r="J34" s="287"/>
-      <c r="K34" s="287"/>
-      <c r="L34" s="287"/>
-      <c r="M34" s="287"/>
-      <c r="N34" s="287"/>
-      <c r="O34" s="287"/>
-      <c r="P34" s="287"/>
-      <c r="Q34" s="287"/>
-      <c r="R34" s="287"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="229"/>
+      <c r="I34" s="229"/>
+      <c r="J34" s="229"/>
+      <c r="K34" s="229"/>
+      <c r="L34" s="229"/>
+      <c r="M34" s="229"/>
+      <c r="N34" s="229"/>
+      <c r="O34" s="229"/>
+      <c r="P34" s="229"/>
+      <c r="Q34" s="229"/>
+      <c r="R34" s="229"/>
     </row>
     <row r="35" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="302" t="s">
+      <c r="C35" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="302"/>
+      <c r="D35" s="303"/>
       <c r="E35" s="127" t="s">
         <v>128</v>
       </c>
@@ -10487,10 +10487,10 @@
       <c r="R35" s="218"/>
     </row>
     <row r="36" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="288" t="s">
+      <c r="B36" s="231" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="237" t="s">
+      <c r="C36" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D36" s="53" t="s">
@@ -10532,15 +10532,15 @@
       <c r="O36" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="P36" s="262" t="s">
+      <c r="P36" s="232" t="s">
         <v>132</v>
       </c>
-      <c r="Q36" s="315"/>
-      <c r="R36" s="263"/>
+      <c r="Q36" s="298"/>
+      <c r="R36" s="233"/>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B37" s="288"/>
-      <c r="C37" s="237"/>
+      <c r="B37" s="231"/>
+      <c r="C37" s="228"/>
       <c r="D37" s="53" t="s">
         <v>22</v>
       </c>
@@ -10580,9 +10580,9 @@
       <c r="O37" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="P37" s="264"/>
-      <c r="Q37" s="316"/>
-      <c r="R37" s="265"/>
+      <c r="P37" s="299"/>
+      <c r="Q37" s="300"/>
+      <c r="R37" s="301"/>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="123" t="s">
@@ -10629,11 +10629,11 @@
       <c r="O38" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="P38" s="308" t="s">
+      <c r="P38" s="295" t="s">
         <v>136</v>
       </c>
-      <c r="Q38" s="309"/>
-      <c r="R38" s="310"/>
+      <c r="Q38" s="296"/>
+      <c r="R38" s="297"/>
     </row>
     <row r="39" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="125" t="s">
@@ -10681,11 +10681,11 @@
       <c r="O39" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="P39" s="308" t="s">
+      <c r="P39" s="295" t="s">
         <v>136</v>
       </c>
-      <c r="Q39" s="309"/>
-      <c r="R39" s="310"/>
+      <c r="Q39" s="296"/>
+      <c r="R39" s="297"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="42"/>
@@ -10728,86 +10728,86 @@
       <c r="S41" s="7"/>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B42" s="221" t="s">
+      <c r="B42" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="221"/>
-      <c r="D42" s="221"/>
-      <c r="E42" s="221"/>
-      <c r="F42" s="221"/>
-      <c r="G42" s="221"/>
-      <c r="H42" s="221"/>
-      <c r="I42" s="221"/>
-      <c r="J42" s="221"/>
-      <c r="K42" s="221"/>
-      <c r="L42" s="221"/>
-      <c r="M42" s="221"/>
-      <c r="N42" s="221"/>
-      <c r="O42" s="221"/>
-      <c r="P42" s="221"/>
-      <c r="Q42" s="221"/>
-      <c r="R42" s="221"/>
-      <c r="S42" s="221"/>
+      <c r="C42" s="239"/>
+      <c r="D42" s="239"/>
+      <c r="E42" s="239"/>
+      <c r="F42" s="239"/>
+      <c r="G42" s="239"/>
+      <c r="H42" s="239"/>
+      <c r="I42" s="239"/>
+      <c r="J42" s="239"/>
+      <c r="K42" s="239"/>
+      <c r="L42" s="239"/>
+      <c r="M42" s="239"/>
+      <c r="N42" s="239"/>
+      <c r="O42" s="239"/>
+      <c r="P42" s="239"/>
+      <c r="Q42" s="239"/>
+      <c r="R42" s="239"/>
+      <c r="S42" s="239"/>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B43" s="221"/>
-      <c r="C43" s="221"/>
-      <c r="D43" s="221"/>
-      <c r="E43" s="221"/>
-      <c r="F43" s="221"/>
-      <c r="G43" s="221"/>
-      <c r="H43" s="221"/>
-      <c r="I43" s="221"/>
-      <c r="J43" s="221"/>
-      <c r="K43" s="221"/>
-      <c r="L43" s="221"/>
-      <c r="M43" s="221"/>
-      <c r="N43" s="221"/>
-      <c r="O43" s="221"/>
-      <c r="P43" s="221"/>
-      <c r="Q43" s="221"/>
-      <c r="R43" s="221"/>
-      <c r="S43" s="221"/>
+      <c r="B43" s="239"/>
+      <c r="C43" s="239"/>
+      <c r="D43" s="239"/>
+      <c r="E43" s="239"/>
+      <c r="F43" s="239"/>
+      <c r="G43" s="239"/>
+      <c r="H43" s="239"/>
+      <c r="I43" s="239"/>
+      <c r="J43" s="239"/>
+      <c r="K43" s="239"/>
+      <c r="L43" s="239"/>
+      <c r="M43" s="239"/>
+      <c r="N43" s="239"/>
+      <c r="O43" s="239"/>
+      <c r="P43" s="239"/>
+      <c r="Q43" s="239"/>
+      <c r="R43" s="239"/>
+      <c r="S43" s="239"/>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B44" s="221"/>
-      <c r="C44" s="221"/>
-      <c r="D44" s="221"/>
-      <c r="E44" s="221"/>
-      <c r="F44" s="221"/>
-      <c r="G44" s="221"/>
-      <c r="H44" s="221"/>
-      <c r="I44" s="221"/>
-      <c r="J44" s="221"/>
-      <c r="K44" s="221"/>
-      <c r="L44" s="221"/>
-      <c r="M44" s="221"/>
-      <c r="N44" s="221"/>
-      <c r="O44" s="221"/>
-      <c r="P44" s="221"/>
-      <c r="Q44" s="221"/>
-      <c r="R44" s="221"/>
-      <c r="S44" s="221"/>
+      <c r="B44" s="239"/>
+      <c r="C44" s="239"/>
+      <c r="D44" s="239"/>
+      <c r="E44" s="239"/>
+      <c r="F44" s="239"/>
+      <c r="G44" s="239"/>
+      <c r="H44" s="239"/>
+      <c r="I44" s="239"/>
+      <c r="J44" s="239"/>
+      <c r="K44" s="239"/>
+      <c r="L44" s="239"/>
+      <c r="M44" s="239"/>
+      <c r="N44" s="239"/>
+      <c r="O44" s="239"/>
+      <c r="P44" s="239"/>
+      <c r="Q44" s="239"/>
+      <c r="R44" s="239"/>
+      <c r="S44" s="239"/>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B45" s="224"/>
-      <c r="C45" s="224"/>
-      <c r="D45" s="224"/>
-      <c r="E45" s="224"/>
-      <c r="F45" s="224"/>
-      <c r="G45" s="224"/>
-      <c r="H45" s="224"/>
-      <c r="I45" s="224"/>
-      <c r="J45" s="224"/>
-      <c r="K45" s="224"/>
-      <c r="L45" s="224"/>
-      <c r="M45" s="224"/>
-      <c r="N45" s="224"/>
-      <c r="O45" s="224"/>
-      <c r="P45" s="224"/>
-      <c r="Q45" s="224"/>
-      <c r="R45" s="224"/>
-      <c r="S45" s="224"/>
+      <c r="B45" s="242"/>
+      <c r="C45" s="242"/>
+      <c r="D45" s="242"/>
+      <c r="E45" s="242"/>
+      <c r="F45" s="242"/>
+      <c r="G45" s="242"/>
+      <c r="H45" s="242"/>
+      <c r="I45" s="242"/>
+      <c r="J45" s="242"/>
+      <c r="K45" s="242"/>
+      <c r="L45" s="242"/>
+      <c r="M45" s="242"/>
+      <c r="N45" s="242"/>
+      <c r="O45" s="242"/>
+      <c r="P45" s="242"/>
+      <c r="Q45" s="242"/>
+      <c r="R45" s="242"/>
+      <c r="S45" s="242"/>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="42"/>
@@ -11033,10 +11033,10 @@
       </c>
     </row>
     <row r="57" spans="2:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="303" t="s">
+      <c r="B57" s="294" t="s">
         <v>143</v>
       </c>
-      <c r="C57" s="304" t="s">
+      <c r="C57" s="302" t="s">
         <v>112</v>
       </c>
       <c r="D57" s="141" t="s">
@@ -11078,7 +11078,7 @@
       <c r="O57" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P57" s="306" t="s">
+      <c r="P57" s="288" t="s">
         <v>73</v>
       </c>
       <c r="Q57" s="141" t="s">
@@ -11086,8 +11086,8 @@
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B58" s="303"/>
-      <c r="C58" s="304"/>
+      <c r="B58" s="294"/>
+      <c r="C58" s="302"/>
       <c r="D58" s="141" t="s">
         <v>22</v>
       </c>
@@ -11127,16 +11127,16 @@
       <c r="O58" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P58" s="307"/>
+      <c r="P58" s="289"/>
       <c r="Q58" s="141" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B59" s="303" t="s">
+      <c r="B59" s="294" t="s">
         <v>144</v>
       </c>
-      <c r="C59" s="304" t="s">
+      <c r="C59" s="302" t="s">
         <v>112</v>
       </c>
       <c r="D59" s="141" t="s">
@@ -11178,14 +11178,14 @@
       <c r="O59" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P59" s="307"/>
+      <c r="P59" s="289"/>
       <c r="Q59" s="141" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="60" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="303"/>
-      <c r="C60" s="304"/>
+      <c r="B60" s="294"/>
+      <c r="C60" s="302"/>
       <c r="D60" s="141" t="s">
         <v>22</v>
       </c>
@@ -11225,16 +11225,16 @@
       <c r="O60" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P60" s="311"/>
+      <c r="P60" s="290"/>
       <c r="Q60" s="141" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="61" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="303" t="s">
+      <c r="B61" s="294" t="s">
         <v>145</v>
       </c>
-      <c r="C61" s="304" t="s">
+      <c r="C61" s="302" t="s">
         <v>112</v>
       </c>
       <c r="D61" s="141" t="s">
@@ -11276,7 +11276,7 @@
       <c r="O61" s="203" t="s">
         <v>58</v>
       </c>
-      <c r="P61" s="312" t="s">
+      <c r="P61" s="291" t="s">
         <v>59</v>
       </c>
       <c r="Q61" s="141" t="s">
@@ -11284,8 +11284,8 @@
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B62" s="303"/>
-      <c r="C62" s="304"/>
+      <c r="B62" s="294"/>
+      <c r="C62" s="302"/>
       <c r="D62" s="141" t="s">
         <v>22</v>
       </c>
@@ -11325,16 +11325,16 @@
       <c r="O62" s="203" t="s">
         <v>58</v>
       </c>
-      <c r="P62" s="313"/>
+      <c r="P62" s="292"/>
       <c r="Q62" s="141" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B63" s="303" t="s">
+      <c r="B63" s="294" t="s">
         <v>147</v>
       </c>
-      <c r="C63" s="304" t="s">
+      <c r="C63" s="302" t="s">
         <v>112</v>
       </c>
       <c r="D63" s="141" t="s">
@@ -11376,14 +11376,14 @@
       <c r="O63" s="203" t="s">
         <v>58</v>
       </c>
-      <c r="P63" s="313"/>
+      <c r="P63" s="292"/>
       <c r="Q63" s="141" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B64" s="303"/>
-      <c r="C64" s="304"/>
+      <c r="B64" s="294"/>
+      <c r="C64" s="302"/>
       <c r="D64" s="141" t="s">
         <v>22</v>
       </c>
@@ -11423,30 +11423,30 @@
       <c r="O64" s="203" t="s">
         <v>58</v>
       </c>
-      <c r="P64" s="314"/>
+      <c r="P64" s="293"/>
       <c r="Q64" s="141" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="65" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="250" t="s">
+      <c r="B65" s="276" t="s">
         <v>148</v>
       </c>
-      <c r="C65" s="250"/>
-      <c r="D65" s="261"/>
-      <c r="E65" s="261"/>
-      <c r="F65" s="250"/>
-      <c r="G65" s="261"/>
-      <c r="H65" s="261"/>
-      <c r="I65" s="250"/>
-      <c r="J65" s="261"/>
-      <c r="K65" s="261"/>
-      <c r="L65" s="261"/>
-      <c r="M65" s="250"/>
-      <c r="N65" s="261"/>
-      <c r="O65" s="261"/>
-      <c r="P65" s="261"/>
-      <c r="Q65" s="261"/>
+      <c r="C65" s="276"/>
+      <c r="D65" s="256"/>
+      <c r="E65" s="256"/>
+      <c r="F65" s="276"/>
+      <c r="G65" s="256"/>
+      <c r="H65" s="256"/>
+      <c r="I65" s="276"/>
+      <c r="J65" s="256"/>
+      <c r="K65" s="256"/>
+      <c r="L65" s="256"/>
+      <c r="M65" s="276"/>
+      <c r="N65" s="256"/>
+      <c r="O65" s="256"/>
+      <c r="P65" s="256"/>
+      <c r="Q65" s="256"/>
     </row>
     <row r="66" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B66" s="97" t="s">
@@ -11497,7 +11497,7 @@
       </c>
     </row>
     <row r="67" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B67" s="276" t="s">
+      <c r="B67" s="268" t="s">
         <v>149</v>
       </c>
       <c r="C67" s="206" t="s">
@@ -11542,7 +11542,7 @@
       <c r="O67" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P67" s="306" t="s">
+      <c r="P67" s="288" t="s">
         <v>73</v>
       </c>
       <c r="Q67" s="147" t="s">
@@ -42998,7 +42998,7 @@
       </c>
     </row>
     <row r="68" spans="2:62 3072:12198 12789:15082" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="305"/>
+      <c r="B68" s="304"/>
       <c r="C68" s="206" t="s">
         <v>112</v>
       </c>
@@ -43041,7 +43041,7 @@
       <c r="O68" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P68" s="307"/>
+      <c r="P68" s="289"/>
       <c r="Q68" s="147" t="s">
         <v>123</v>
       </c>
@@ -54581,7 +54581,7 @@
       </c>
     </row>
     <row r="71" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B71" s="276" t="s">
+      <c r="B71" s="268" t="s">
         <v>151</v>
       </c>
       <c r="C71" s="206" t="s">
@@ -54626,7 +54626,7 @@
       <c r="O71" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P71" s="306" t="s">
+      <c r="P71" s="288" t="s">
         <v>73</v>
       </c>
       <c r="Q71" s="147" t="s">
@@ -54634,7 +54634,7 @@
       </c>
     </row>
     <row r="72" spans="2:62 3072:12198 12789:15082" x14ac:dyDescent="0.3">
-      <c r="B72" s="305"/>
+      <c r="B72" s="304"/>
       <c r="C72" s="206" t="s">
         <v>112</v>
       </c>
@@ -54677,41 +54677,41 @@
       <c r="O72" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P72" s="307"/>
+      <c r="P72" s="289"/>
       <c r="Q72" s="147" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="79" spans="2:62 3072:12198 12789:15082" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B79" s="249" t="s">
+      <c r="B79" s="223" t="s">
         <v>153</v>
       </c>
-      <c r="C79" s="249"/>
-      <c r="D79" s="249"/>
-      <c r="E79" s="249"/>
-      <c r="F79" s="249"/>
-      <c r="G79" s="249"/>
-      <c r="H79" s="249"/>
-      <c r="I79" s="249"/>
-      <c r="J79" s="249"/>
-      <c r="K79" s="249"/>
-      <c r="L79" s="249"/>
-      <c r="M79" s="249"/>
-      <c r="N79" s="249"/>
-      <c r="O79" s="249"/>
-      <c r="P79" s="249"/>
-      <c r="Q79" s="249"/>
-      <c r="R79" s="249"/>
-      <c r="S79" s="249"/>
+      <c r="C79" s="223"/>
+      <c r="D79" s="223"/>
+      <c r="E79" s="223"/>
+      <c r="F79" s="223"/>
+      <c r="G79" s="223"/>
+      <c r="H79" s="223"/>
+      <c r="I79" s="223"/>
+      <c r="J79" s="223"/>
+      <c r="K79" s="223"/>
+      <c r="L79" s="223"/>
+      <c r="M79" s="223"/>
+      <c r="N79" s="223"/>
+      <c r="O79" s="223"/>
+      <c r="P79" s="223"/>
+      <c r="Q79" s="223"/>
+      <c r="R79" s="223"/>
+      <c r="S79" s="223"/>
     </row>
     <row r="80" spans="2:62 3072:12198 12789:15082" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C80" s="302" t="s">
+      <c r="C80" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D80" s="302"/>
+      <c r="D80" s="303"/>
       <c r="E80" s="127" t="s">
         <v>128</v>
       </c>
@@ -54755,10 +54755,10 @@
       <c r="S80" s="218"/>
     </row>
     <row r="81" spans="2:20" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="253" t="s">
+      <c r="B81" s="221" t="s">
         <v>90</v>
       </c>
-      <c r="C81" s="237" t="s">
+      <c r="C81" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D81" s="53" t="s">
@@ -54802,15 +54802,15 @@
       <c r="P81" s="53" t="s">
         <v>156</v>
       </c>
-      <c r="Q81" s="238" t="s">
+      <c r="Q81" s="236" t="s">
         <v>44</v>
       </c>
-      <c r="R81" s="238"/>
-      <c r="S81" s="238"/>
+      <c r="R81" s="236"/>
+      <c r="S81" s="236"/>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B82" s="220"/>
-      <c r="C82" s="237"/>
+      <c r="C82" s="228"/>
       <c r="D82" s="53" t="s">
         <v>22</v>
       </c>
@@ -54852,9 +54852,9 @@
       <c r="P82" s="53" t="s">
         <v>156</v>
       </c>
-      <c r="Q82" s="238"/>
-      <c r="R82" s="238"/>
-      <c r="S82" s="238"/>
+      <c r="Q82" s="236"/>
+      <c r="R82" s="236"/>
+      <c r="S82" s="236"/>
     </row>
     <row r="84" spans="2:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
@@ -54880,90 +54880,90 @@
       <c r="T84" s="6"/>
     </row>
     <row r="85" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B85" s="280" t="s">
+      <c r="B85" s="238" t="s">
         <v>33</v>
       </c>
-      <c r="C85" s="280"/>
-      <c r="D85" s="280"/>
-      <c r="E85" s="280"/>
-      <c r="F85" s="280"/>
-      <c r="G85" s="280"/>
-      <c r="H85" s="280"/>
-      <c r="I85" s="280"/>
-      <c r="J85" s="280"/>
-      <c r="K85" s="280"/>
-      <c r="L85" s="280"/>
-      <c r="M85" s="280"/>
-      <c r="N85" s="280"/>
-      <c r="O85" s="280"/>
-      <c r="P85" s="280"/>
-      <c r="Q85" s="280"/>
-      <c r="R85" s="280"/>
-      <c r="S85" s="280"/>
-      <c r="T85" s="280"/>
+      <c r="C85" s="238"/>
+      <c r="D85" s="238"/>
+      <c r="E85" s="238"/>
+      <c r="F85" s="238"/>
+      <c r="G85" s="238"/>
+      <c r="H85" s="238"/>
+      <c r="I85" s="238"/>
+      <c r="J85" s="238"/>
+      <c r="K85" s="238"/>
+      <c r="L85" s="238"/>
+      <c r="M85" s="238"/>
+      <c r="N85" s="238"/>
+      <c r="O85" s="238"/>
+      <c r="P85" s="238"/>
+      <c r="Q85" s="238"/>
+      <c r="R85" s="238"/>
+      <c r="S85" s="238"/>
+      <c r="T85" s="238"/>
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B86" s="280"/>
-      <c r="C86" s="280"/>
-      <c r="D86" s="280"/>
-      <c r="E86" s="280"/>
-      <c r="F86" s="280"/>
-      <c r="G86" s="280"/>
-      <c r="H86" s="280"/>
-      <c r="I86" s="280"/>
-      <c r="J86" s="280"/>
-      <c r="K86" s="280"/>
-      <c r="L86" s="280"/>
-      <c r="M86" s="280"/>
-      <c r="N86" s="280"/>
-      <c r="O86" s="280"/>
-      <c r="P86" s="280"/>
-      <c r="Q86" s="280"/>
-      <c r="R86" s="280"/>
-      <c r="S86" s="280"/>
-      <c r="T86" s="280"/>
+      <c r="B86" s="238"/>
+      <c r="C86" s="238"/>
+      <c r="D86" s="238"/>
+      <c r="E86" s="238"/>
+      <c r="F86" s="238"/>
+      <c r="G86" s="238"/>
+      <c r="H86" s="238"/>
+      <c r="I86" s="238"/>
+      <c r="J86" s="238"/>
+      <c r="K86" s="238"/>
+      <c r="L86" s="238"/>
+      <c r="M86" s="238"/>
+      <c r="N86" s="238"/>
+      <c r="O86" s="238"/>
+      <c r="P86" s="238"/>
+      <c r="Q86" s="238"/>
+      <c r="R86" s="238"/>
+      <c r="S86" s="238"/>
+      <c r="T86" s="238"/>
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B87" s="280"/>
-      <c r="C87" s="280"/>
-      <c r="D87" s="280"/>
-      <c r="E87" s="280"/>
-      <c r="F87" s="280"/>
-      <c r="G87" s="280"/>
-      <c r="H87" s="280"/>
-      <c r="I87" s="280"/>
-      <c r="J87" s="280"/>
-      <c r="K87" s="280"/>
-      <c r="L87" s="280"/>
-      <c r="M87" s="280"/>
-      <c r="N87" s="280"/>
-      <c r="O87" s="280"/>
-      <c r="P87" s="280"/>
-      <c r="Q87" s="280"/>
-      <c r="R87" s="280"/>
-      <c r="S87" s="280"/>
-      <c r="T87" s="280"/>
+      <c r="B87" s="238"/>
+      <c r="C87" s="238"/>
+      <c r="D87" s="238"/>
+      <c r="E87" s="238"/>
+      <c r="F87" s="238"/>
+      <c r="G87" s="238"/>
+      <c r="H87" s="238"/>
+      <c r="I87" s="238"/>
+      <c r="J87" s="238"/>
+      <c r="K87" s="238"/>
+      <c r="L87" s="238"/>
+      <c r="M87" s="238"/>
+      <c r="N87" s="238"/>
+      <c r="O87" s="238"/>
+      <c r="P87" s="238"/>
+      <c r="Q87" s="238"/>
+      <c r="R87" s="238"/>
+      <c r="S87" s="238"/>
+      <c r="T87" s="238"/>
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B88" s="280"/>
-      <c r="C88" s="280"/>
-      <c r="D88" s="280"/>
-      <c r="E88" s="280"/>
-      <c r="F88" s="280"/>
-      <c r="G88" s="280"/>
-      <c r="H88" s="280"/>
-      <c r="I88" s="280"/>
-      <c r="J88" s="280"/>
-      <c r="K88" s="280"/>
-      <c r="L88" s="280"/>
-      <c r="M88" s="280"/>
-      <c r="N88" s="280"/>
-      <c r="O88" s="280"/>
-      <c r="P88" s="280"/>
-      <c r="Q88" s="280"/>
-      <c r="R88" s="280"/>
-      <c r="S88" s="280"/>
-      <c r="T88" s="280"/>
+      <c r="B88" s="238"/>
+      <c r="C88" s="238"/>
+      <c r="D88" s="238"/>
+      <c r="E88" s="238"/>
+      <c r="F88" s="238"/>
+      <c r="G88" s="238"/>
+      <c r="H88" s="238"/>
+      <c r="I88" s="238"/>
+      <c r="J88" s="238"/>
+      <c r="K88" s="238"/>
+      <c r="L88" s="238"/>
+      <c r="M88" s="238"/>
+      <c r="N88" s="238"/>
+      <c r="O88" s="238"/>
+      <c r="P88" s="238"/>
+      <c r="Q88" s="238"/>
+      <c r="R88" s="238"/>
+      <c r="S88" s="238"/>
+      <c r="T88" s="238"/>
     </row>
     <row r="98" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="99" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -55035,10 +55035,10 @@
       </c>
     </row>
     <row r="101" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B101" s="290" t="s">
+      <c r="B101" s="305" t="s">
         <v>158</v>
       </c>
-      <c r="C101" s="237" t="s">
+      <c r="C101" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D101" s="53" t="s">
@@ -55087,8 +55087,8 @@
       </c>
     </row>
     <row r="102" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B102" s="290"/>
-      <c r="C102" s="237"/>
+      <c r="B102" s="305"/>
+      <c r="C102" s="228"/>
       <c r="D102" s="53" t="s">
         <v>22</v>
       </c>
@@ -55204,10 +55204,10 @@
       </c>
     </row>
     <row r="114" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B114" s="290" t="s">
+      <c r="B114" s="305" t="s">
         <v>163</v>
       </c>
-      <c r="C114" s="237" t="s">
+      <c r="C114" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D114" s="53" t="s">
@@ -55256,10 +55256,10 @@
       </c>
     </row>
     <row r="115" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B115" s="290" t="s">
+      <c r="B115" s="305" t="s">
         <v>163</v>
       </c>
-      <c r="C115" s="237" t="s">
+      <c r="C115" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D115" s="53" t="s">
@@ -55308,10 +55308,10 @@
       </c>
     </row>
     <row r="116" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B116" s="290" t="s">
+      <c r="B116" s="305" t="s">
         <v>164</v>
       </c>
-      <c r="C116" s="237" t="s">
+      <c r="C116" s="228" t="s">
         <v>112</v>
       </c>
       <c r="D116" s="53" t="s">
@@ -55361,8 +55361,8 @@
       </c>
     </row>
     <row r="117" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B117" s="290"/>
-      <c r="C117" s="237"/>
+      <c r="B117" s="305"/>
+      <c r="C117" s="228"/>
       <c r="D117" s="53" t="s">
         <v>22</v>
       </c>
@@ -55411,19 +55411,35 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="P57:P60"/>
-    <mergeCell ref="P61:P64"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="P36:R37"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="B20:R20"/>
+    <mergeCell ref="B21:R24"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="Q81:S82"/>
+    <mergeCell ref="B85:T88"/>
+    <mergeCell ref="B99:Q99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="B112:Q112"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="Q80:S80"/>
+    <mergeCell ref="B79:S79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="P67:P68"/>
+    <mergeCell ref="P71:P72"/>
     <mergeCell ref="B9:Q9"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="B13:B14"/>
@@ -55440,35 +55456,19 @@
     <mergeCell ref="B59:B60"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P71:P72"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="B65:Q65"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B112:Q112"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="Q80:S80"/>
-    <mergeCell ref="B79:S79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="B20:R20"/>
-    <mergeCell ref="B21:R24"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="Q81:S82"/>
-    <mergeCell ref="B85:T88"/>
-    <mergeCell ref="B99:Q99"/>
-    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="P61:P64"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="P36:R37"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55479,7 +55479,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6411E299-5866-CE44-ADC7-A0E34965AEA2}">
-  <dimension ref="B8:S114"/>
+  <dimension ref="B8:R114"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="19"/>
@@ -55505,8 +55505,8 @@
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="126"/>
       <c r="C8" s="126"/>
-      <c r="D8" s="317"/>
-      <c r="E8" s="317"/>
+      <c r="D8" s="319"/>
+      <c r="E8" s="319"/>
       <c r="F8" s="126"/>
       <c r="G8" s="126"/>
       <c r="H8" s="126"/>
@@ -55544,10 +55544,10 @@
       <c r="B10" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="318" t="s">
+      <c r="C10" s="338" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="319"/>
+      <c r="D10" s="339"/>
       <c r="E10" s="12" t="s">
         <v>3</v>
       </c>
@@ -55587,10 +55587,10 @@
       <c r="Q10" s="126"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B11" s="320" t="s">
+      <c r="B11" s="340" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="320" t="s">
+      <c r="C11" s="340" t="s">
         <v>169</v>
       </c>
       <c r="D11" s="41" t="s">
@@ -55638,8 +55638,8 @@
       <c r="Q11" s="126"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12" s="321"/>
-      <c r="C12" s="321"/>
+      <c r="B12" s="341"/>
+      <c r="C12" s="341"/>
       <c r="D12" s="41" t="s">
         <v>22</v>
       </c>
@@ -55685,10 +55685,10 @@
       <c r="Q12" s="126"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="320" t="s">
+      <c r="B13" s="340" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="320" t="s">
+      <c r="C13" s="340" t="s">
         <v>169</v>
       </c>
       <c r="D13" s="41" t="s">
@@ -55736,8 +55736,8 @@
       <c r="Q13" s="126"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14" s="321"/>
-      <c r="C14" s="321"/>
+      <c r="B14" s="341"/>
+      <c r="C14" s="341"/>
       <c r="D14" s="41" t="s">
         <v>22</v>
       </c>
@@ -55783,10 +55783,10 @@
       <c r="Q14" s="126"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="320" t="s">
+      <c r="B15" s="340" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="320" t="s">
+      <c r="C15" s="340" t="s">
         <v>169</v>
       </c>
       <c r="D15" s="41" t="s">
@@ -55834,8 +55834,8 @@
       <c r="Q15" s="126"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B16" s="321"/>
-      <c r="C16" s="321"/>
+      <c r="B16" s="341"/>
+      <c r="C16" s="341"/>
       <c r="D16" s="41" t="s">
         <v>22</v>
       </c>
@@ -55895,93 +55895,93 @@
       <c r="N17" s="34"/>
     </row>
     <row r="18" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="326" t="s">
+      <c r="B18" s="344" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="327"/>
-      <c r="D18" s="327"/>
-      <c r="E18" s="327"/>
-      <c r="F18" s="327"/>
-      <c r="G18" s="327"/>
-      <c r="H18" s="327"/>
-      <c r="I18" s="327"/>
-      <c r="J18" s="327"/>
-      <c r="K18" s="327"/>
-      <c r="L18" s="327"/>
-      <c r="M18" s="327"/>
-      <c r="N18" s="327"/>
-      <c r="O18" s="327"/>
-      <c r="P18" s="328"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
+      <c r="G18" s="345"/>
+      <c r="H18" s="345"/>
+      <c r="I18" s="345"/>
+      <c r="J18" s="345"/>
+      <c r="K18" s="345"/>
+      <c r="L18" s="345"/>
+      <c r="M18" s="345"/>
+      <c r="N18" s="345"/>
+      <c r="O18" s="345"/>
+      <c r="P18" s="346"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="294" t="s">
+      <c r="B19" s="309" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="295"/>
-      <c r="D19" s="295"/>
-      <c r="E19" s="295"/>
-      <c r="F19" s="295"/>
-      <c r="G19" s="295"/>
-      <c r="H19" s="295"/>
-      <c r="I19" s="295"/>
-      <c r="J19" s="295"/>
-      <c r="K19" s="295"/>
-      <c r="L19" s="295"/>
-      <c r="M19" s="295"/>
-      <c r="N19" s="295"/>
-      <c r="O19" s="295"/>
-      <c r="P19" s="296"/>
+      <c r="C19" s="310"/>
+      <c r="D19" s="310"/>
+      <c r="E19" s="310"/>
+      <c r="F19" s="310"/>
+      <c r="G19" s="310"/>
+      <c r="H19" s="310"/>
+      <c r="I19" s="310"/>
+      <c r="J19" s="310"/>
+      <c r="K19" s="310"/>
+      <c r="L19" s="310"/>
+      <c r="M19" s="310"/>
+      <c r="N19" s="310"/>
+      <c r="O19" s="310"/>
+      <c r="P19" s="311"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="297"/>
-      <c r="C20" s="231"/>
-      <c r="D20" s="231"/>
-      <c r="E20" s="231"/>
-      <c r="F20" s="231"/>
-      <c r="G20" s="231"/>
-      <c r="H20" s="231"/>
-      <c r="I20" s="231"/>
-      <c r="J20" s="231"/>
-      <c r="K20" s="231"/>
-      <c r="L20" s="231"/>
-      <c r="M20" s="231"/>
-      <c r="N20" s="231"/>
-      <c r="O20" s="231"/>
-      <c r="P20" s="298"/>
+      <c r="B20" s="312"/>
+      <c r="C20" s="282"/>
+      <c r="D20" s="282"/>
+      <c r="E20" s="282"/>
+      <c r="F20" s="282"/>
+      <c r="G20" s="282"/>
+      <c r="H20" s="282"/>
+      <c r="I20" s="282"/>
+      <c r="J20" s="282"/>
+      <c r="K20" s="282"/>
+      <c r="L20" s="282"/>
+      <c r="M20" s="282"/>
+      <c r="N20" s="282"/>
+      <c r="O20" s="282"/>
+      <c r="P20" s="313"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="297"/>
-      <c r="C21" s="231"/>
-      <c r="D21" s="231"/>
-      <c r="E21" s="231"/>
-      <c r="F21" s="231"/>
-      <c r="G21" s="231"/>
-      <c r="H21" s="231"/>
-      <c r="I21" s="231"/>
-      <c r="J21" s="231"/>
-      <c r="K21" s="231"/>
-      <c r="L21" s="231"/>
-      <c r="M21" s="231"/>
-      <c r="N21" s="231"/>
-      <c r="O21" s="231"/>
-      <c r="P21" s="298"/>
+      <c r="B21" s="312"/>
+      <c r="C21" s="282"/>
+      <c r="D21" s="282"/>
+      <c r="E21" s="282"/>
+      <c r="F21" s="282"/>
+      <c r="G21" s="282"/>
+      <c r="H21" s="282"/>
+      <c r="I21" s="282"/>
+      <c r="J21" s="282"/>
+      <c r="K21" s="282"/>
+      <c r="L21" s="282"/>
+      <c r="M21" s="282"/>
+      <c r="N21" s="282"/>
+      <c r="O21" s="282"/>
+      <c r="P21" s="313"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="299"/>
-      <c r="C22" s="300"/>
-      <c r="D22" s="300"/>
-      <c r="E22" s="300"/>
-      <c r="F22" s="300"/>
-      <c r="G22" s="300"/>
-      <c r="H22" s="300"/>
-      <c r="I22" s="300"/>
-      <c r="J22" s="300"/>
-      <c r="K22" s="300"/>
-      <c r="L22" s="300"/>
-      <c r="M22" s="300"/>
-      <c r="N22" s="300"/>
-      <c r="O22" s="300"/>
-      <c r="P22" s="301"/>
+      <c r="B22" s="314"/>
+      <c r="C22" s="315"/>
+      <c r="D22" s="315"/>
+      <c r="E22" s="315"/>
+      <c r="F22" s="315"/>
+      <c r="G22" s="315"/>
+      <c r="H22" s="315"/>
+      <c r="I22" s="315"/>
+      <c r="J22" s="315"/>
+      <c r="K22" s="315"/>
+      <c r="L22" s="315"/>
+      <c r="M22" s="315"/>
+      <c r="N22" s="315"/>
+      <c r="O22" s="315"/>
+      <c r="P22" s="316"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="27"/>
@@ -56111,33 +56111,33 @@
       <c r="N31" s="34"/>
     </row>
     <row r="32" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="323" t="s">
+      <c r="B32" s="342" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="324"/>
-      <c r="D32" s="324"/>
-      <c r="E32" s="324"/>
-      <c r="F32" s="324"/>
-      <c r="G32" s="324"/>
-      <c r="H32" s="324"/>
-      <c r="I32" s="324"/>
-      <c r="J32" s="324"/>
-      <c r="K32" s="324"/>
-      <c r="L32" s="324"/>
-      <c r="M32" s="324"/>
-      <c r="N32" s="324"/>
-      <c r="O32" s="324"/>
-      <c r="P32" s="324"/>
-      <c r="Q32" s="325"/>
+      <c r="C32" s="321"/>
+      <c r="D32" s="321"/>
+      <c r="E32" s="321"/>
+      <c r="F32" s="321"/>
+      <c r="G32" s="321"/>
+      <c r="H32" s="321"/>
+      <c r="I32" s="321"/>
+      <c r="J32" s="321"/>
+      <c r="K32" s="321"/>
+      <c r="L32" s="321"/>
+      <c r="M32" s="321"/>
+      <c r="N32" s="321"/>
+      <c r="O32" s="321"/>
+      <c r="P32" s="321"/>
+      <c r="Q32" s="343"/>
     </row>
     <row r="33" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B33" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="329" t="s">
+      <c r="C33" s="337" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="329"/>
+      <c r="D33" s="337"/>
       <c r="E33" s="127" t="s">
         <v>128</v>
       </c>
@@ -56171,16 +56171,16 @@
       <c r="O33" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="P33" s="240" t="s">
+      <c r="P33" s="273" t="s">
         <v>36</v>
       </c>
-      <c r="Q33" s="241"/>
+      <c r="Q33" s="274"/>
     </row>
     <row r="34" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="334" t="s">
+      <c r="B34" s="335" t="s">
         <v>177</v>
       </c>
-      <c r="C34" s="335" t="s">
+      <c r="C34" s="336" t="s">
         <v>169</v>
       </c>
       <c r="D34" s="40" t="s">
@@ -56221,14 +56221,14 @@
       <c r="O34" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P34" s="262" t="s">
+      <c r="P34" s="232" t="s">
         <v>178</v>
       </c>
-      <c r="Q34" s="263"/>
+      <c r="Q34" s="233"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B35" s="334"/>
-      <c r="C35" s="335"/>
+      <c r="B35" s="335"/>
+      <c r="C35" s="336"/>
       <c r="D35" s="40" t="s">
         <v>22</v>
       </c>
@@ -56267,8 +56267,8 @@
       <c r="O35" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P35" s="264"/>
-      <c r="Q35" s="265"/>
+      <c r="P35" s="299"/>
+      <c r="Q35" s="301"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B36" s="119" t="s">
@@ -56315,8 +56315,8 @@
       <c r="O36" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="P36" s="266"/>
-      <c r="Q36" s="267"/>
+      <c r="P36" s="234"/>
+      <c r="Q36" s="235"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B37" s="72"/>
@@ -56369,74 +56369,74 @@
       <c r="P39" s="7"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B40" s="221" t="s">
+      <c r="B40" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="222"/>
-      <c r="D40" s="222"/>
-      <c r="E40" s="222"/>
-      <c r="F40" s="222"/>
-      <c r="G40" s="222"/>
-      <c r="H40" s="222"/>
-      <c r="I40" s="222"/>
-      <c r="J40" s="222"/>
-      <c r="K40" s="222"/>
-      <c r="L40" s="222"/>
-      <c r="M40" s="222"/>
-      <c r="N40" s="222"/>
-      <c r="O40" s="222"/>
-      <c r="P40" s="223"/>
+      <c r="C40" s="240"/>
+      <c r="D40" s="240"/>
+      <c r="E40" s="240"/>
+      <c r="F40" s="240"/>
+      <c r="G40" s="240"/>
+      <c r="H40" s="240"/>
+      <c r="I40" s="240"/>
+      <c r="J40" s="240"/>
+      <c r="K40" s="240"/>
+      <c r="L40" s="240"/>
+      <c r="M40" s="240"/>
+      <c r="N40" s="240"/>
+      <c r="O40" s="240"/>
+      <c r="P40" s="241"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B41" s="221"/>
-      <c r="C41" s="222"/>
-      <c r="D41" s="222"/>
-      <c r="E41" s="222"/>
-      <c r="F41" s="222"/>
-      <c r="G41" s="222"/>
-      <c r="H41" s="222"/>
-      <c r="I41" s="222"/>
-      <c r="J41" s="222"/>
-      <c r="K41" s="222"/>
-      <c r="L41" s="222"/>
-      <c r="M41" s="222"/>
-      <c r="N41" s="222"/>
-      <c r="O41" s="222"/>
-      <c r="P41" s="223"/>
+      <c r="B41" s="239"/>
+      <c r="C41" s="240"/>
+      <c r="D41" s="240"/>
+      <c r="E41" s="240"/>
+      <c r="F41" s="240"/>
+      <c r="G41" s="240"/>
+      <c r="H41" s="240"/>
+      <c r="I41" s="240"/>
+      <c r="J41" s="240"/>
+      <c r="K41" s="240"/>
+      <c r="L41" s="240"/>
+      <c r="M41" s="240"/>
+      <c r="N41" s="240"/>
+      <c r="O41" s="240"/>
+      <c r="P41" s="241"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B42" s="221"/>
-      <c r="C42" s="222"/>
-      <c r="D42" s="222"/>
-      <c r="E42" s="222"/>
-      <c r="F42" s="222"/>
-      <c r="G42" s="222"/>
-      <c r="H42" s="222"/>
-      <c r="I42" s="222"/>
-      <c r="J42" s="222"/>
-      <c r="K42" s="222"/>
-      <c r="L42" s="222"/>
-      <c r="M42" s="222"/>
-      <c r="N42" s="222"/>
-      <c r="O42" s="222"/>
-      <c r="P42" s="223"/>
+      <c r="B42" s="239"/>
+      <c r="C42" s="240"/>
+      <c r="D42" s="240"/>
+      <c r="E42" s="240"/>
+      <c r="F42" s="240"/>
+      <c r="G42" s="240"/>
+      <c r="H42" s="240"/>
+      <c r="I42" s="240"/>
+      <c r="J42" s="240"/>
+      <c r="K42" s="240"/>
+      <c r="L42" s="240"/>
+      <c r="M42" s="240"/>
+      <c r="N42" s="240"/>
+      <c r="O42" s="240"/>
+      <c r="P42" s="241"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B43" s="224"/>
-      <c r="C43" s="225"/>
-      <c r="D43" s="225"/>
-      <c r="E43" s="225"/>
-      <c r="F43" s="225"/>
-      <c r="G43" s="225"/>
-      <c r="H43" s="225"/>
-      <c r="I43" s="225"/>
-      <c r="J43" s="225"/>
-      <c r="K43" s="225"/>
-      <c r="L43" s="225"/>
-      <c r="M43" s="225"/>
-      <c r="N43" s="225"/>
-      <c r="O43" s="225"/>
-      <c r="P43" s="226"/>
+      <c r="B43" s="242"/>
+      <c r="C43" s="243"/>
+      <c r="D43" s="243"/>
+      <c r="E43" s="243"/>
+      <c r="F43" s="243"/>
+      <c r="G43" s="243"/>
+      <c r="H43" s="243"/>
+      <c r="I43" s="243"/>
+      <c r="J43" s="243"/>
+      <c r="K43" s="243"/>
+      <c r="L43" s="243"/>
+      <c r="M43" s="243"/>
+      <c r="N43" s="243"/>
+      <c r="O43" s="243"/>
+      <c r="P43" s="244"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B44" s="42"/>
@@ -56551,24 +56551,24 @@
       <c r="O51" s="126"/>
     </row>
     <row r="52" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="331" t="s">
+      <c r="B52" s="332" t="s">
         <v>182</v>
       </c>
-      <c r="C52" s="332"/>
-      <c r="D52" s="332"/>
-      <c r="E52" s="332"/>
-      <c r="F52" s="332"/>
-      <c r="G52" s="332"/>
-      <c r="H52" s="332"/>
-      <c r="I52" s="332"/>
-      <c r="J52" s="332"/>
-      <c r="K52" s="332"/>
-      <c r="L52" s="332"/>
-      <c r="M52" s="332"/>
-      <c r="N52" s="332"/>
-      <c r="O52" s="332"/>
-      <c r="P52" s="332"/>
-      <c r="Q52" s="333"/>
+      <c r="C52" s="333"/>
+      <c r="D52" s="333"/>
+      <c r="E52" s="333"/>
+      <c r="F52" s="333"/>
+      <c r="G52" s="333"/>
+      <c r="H52" s="333"/>
+      <c r="I52" s="333"/>
+      <c r="J52" s="333"/>
+      <c r="K52" s="333"/>
+      <c r="L52" s="333"/>
+      <c r="M52" s="333"/>
+      <c r="N52" s="333"/>
+      <c r="O52" s="333"/>
+      <c r="P52" s="333"/>
+      <c r="Q52" s="334"/>
     </row>
     <row r="53" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="97" t="s">
@@ -56622,7 +56622,7 @@
       <c r="B54" s="219" t="s">
         <v>183</v>
       </c>
-      <c r="C54" s="330" t="s">
+      <c r="C54" s="317" t="s">
         <v>169</v>
       </c>
       <c r="D54" s="53" t="s">
@@ -56673,7 +56673,7 @@
     </row>
     <row r="55" spans="2:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="219"/>
-      <c r="C55" s="330"/>
+      <c r="C55" s="317"/>
       <c r="D55" s="53" t="s">
         <v>22</v>
       </c>
@@ -56721,24 +56721,24 @@
       </c>
     </row>
     <row r="56" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="331" t="s">
+      <c r="B56" s="332" t="s">
         <v>185</v>
       </c>
-      <c r="C56" s="332"/>
-      <c r="D56" s="332"/>
-      <c r="E56" s="332"/>
-      <c r="F56" s="332"/>
-      <c r="G56" s="332"/>
-      <c r="H56" s="332"/>
-      <c r="I56" s="332"/>
-      <c r="J56" s="332"/>
-      <c r="K56" s="332"/>
-      <c r="L56" s="332"/>
-      <c r="M56" s="332"/>
-      <c r="N56" s="332"/>
-      <c r="O56" s="332"/>
-      <c r="P56" s="332"/>
-      <c r="Q56" s="333"/>
+      <c r="C56" s="333"/>
+      <c r="D56" s="333"/>
+      <c r="E56" s="333"/>
+      <c r="F56" s="333"/>
+      <c r="G56" s="333"/>
+      <c r="H56" s="333"/>
+      <c r="I56" s="333"/>
+      <c r="J56" s="333"/>
+      <c r="K56" s="333"/>
+      <c r="L56" s="333"/>
+      <c r="M56" s="333"/>
+      <c r="N56" s="333"/>
+      <c r="O56" s="333"/>
+      <c r="P56" s="333"/>
+      <c r="Q56" s="334"/>
     </row>
     <row r="57" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
@@ -56792,7 +56792,7 @@
       <c r="B58" s="219" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="330" t="s">
+      <c r="C58" s="317" t="s">
         <v>169</v>
       </c>
       <c r="D58" s="53" t="s">
@@ -56837,13 +56837,13 @@
       <c r="P58" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q58" s="339" t="s">
+      <c r="Q58" s="328" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B59" s="219"/>
-      <c r="C59" s="330"/>
+      <c r="C59" s="317"/>
       <c r="D59" s="53" t="s">
         <v>22</v>
       </c>
@@ -56886,36 +56886,36 @@
       <c r="P59" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q59" s="340"/>
+      <c r="Q59" s="329"/>
     </row>
     <row r="60" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="336" t="s">
+      <c r="B60" s="320" t="s">
         <v>187</v>
       </c>
-      <c r="C60" s="324"/>
-      <c r="D60" s="324"/>
-      <c r="E60" s="324"/>
-      <c r="F60" s="324"/>
-      <c r="G60" s="324"/>
-      <c r="H60" s="324"/>
-      <c r="I60" s="324"/>
-      <c r="J60" s="324"/>
-      <c r="K60" s="324"/>
-      <c r="L60" s="324"/>
-      <c r="M60" s="324"/>
-      <c r="N60" s="324"/>
-      <c r="O60" s="324"/>
-      <c r="P60" s="324"/>
-      <c r="Q60" s="337"/>
+      <c r="C60" s="321"/>
+      <c r="D60" s="321"/>
+      <c r="E60" s="321"/>
+      <c r="F60" s="321"/>
+      <c r="G60" s="321"/>
+      <c r="H60" s="321"/>
+      <c r="I60" s="321"/>
+      <c r="J60" s="321"/>
+      <c r="K60" s="321"/>
+      <c r="L60" s="321"/>
+      <c r="M60" s="321"/>
+      <c r="N60" s="321"/>
+      <c r="O60" s="321"/>
+      <c r="P60" s="321"/>
+      <c r="Q60" s="323"/>
     </row>
     <row r="61" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B61" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C61" s="302" t="s">
+      <c r="C61" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="302"/>
+      <c r="D61" s="303"/>
       <c r="E61" s="8" t="s">
         <v>3</v>
       </c>
@@ -56957,10 +56957,10 @@
       </c>
     </row>
     <row r="62" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="338" t="s">
+      <c r="B62" s="327" t="s">
         <v>188</v>
       </c>
-      <c r="C62" s="330" t="s">
+      <c r="C62" s="317" t="s">
         <v>169</v>
       </c>
       <c r="D62" s="53" t="s">
@@ -57005,13 +57005,13 @@
       <c r="P62" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q62" s="339" t="s">
+      <c r="Q62" s="328" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B63" s="338"/>
-      <c r="C63" s="330"/>
+      <c r="B63" s="327"/>
+      <c r="C63" s="317"/>
       <c r="D63" s="53" t="s">
         <v>22</v>
       </c>
@@ -57054,36 +57054,36 @@
       <c r="P63" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q63" s="340"/>
+      <c r="Q63" s="329"/>
     </row>
     <row r="64" spans="2:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="336" t="s">
+      <c r="B64" s="320" t="s">
         <v>189</v>
       </c>
-      <c r="C64" s="324"/>
-      <c r="D64" s="324"/>
-      <c r="E64" s="324"/>
-      <c r="F64" s="324"/>
-      <c r="G64" s="324"/>
-      <c r="H64" s="324"/>
-      <c r="I64" s="324"/>
-      <c r="J64" s="324"/>
-      <c r="K64" s="324"/>
-      <c r="L64" s="324"/>
-      <c r="M64" s="324"/>
-      <c r="N64" s="324"/>
-      <c r="O64" s="324"/>
-      <c r="P64" s="324"/>
-      <c r="Q64" s="337"/>
+      <c r="C64" s="321"/>
+      <c r="D64" s="321"/>
+      <c r="E64" s="321"/>
+      <c r="F64" s="321"/>
+      <c r="G64" s="321"/>
+      <c r="H64" s="321"/>
+      <c r="I64" s="321"/>
+      <c r="J64" s="321"/>
+      <c r="K64" s="321"/>
+      <c r="L64" s="321"/>
+      <c r="M64" s="321"/>
+      <c r="N64" s="321"/>
+      <c r="O64" s="321"/>
+      <c r="P64" s="321"/>
+      <c r="Q64" s="323"/>
     </row>
     <row r="65" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B65" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="302" t="s">
+      <c r="C65" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="302"/>
+      <c r="D65" s="303"/>
       <c r="E65" s="8" t="s">
         <v>3</v>
       </c>
@@ -57125,10 +57125,10 @@
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B66" s="338" t="s">
+      <c r="B66" s="327" t="s">
         <v>190</v>
       </c>
-      <c r="C66" s="330" t="s">
+      <c r="C66" s="317" t="s">
         <v>169</v>
       </c>
       <c r="D66" s="53" t="s">
@@ -57173,13 +57173,13 @@
       <c r="P66" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q66" s="341" t="s">
+      <c r="Q66" s="325" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B67" s="338"/>
-      <c r="C67" s="330"/>
+      <c r="B67" s="327"/>
+      <c r="C67" s="317"/>
       <c r="D67" s="53" t="s">
         <v>22</v>
       </c>
@@ -57222,36 +57222,36 @@
       <c r="P67" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q67" s="342"/>
+      <c r="Q67" s="330"/>
     </row>
     <row r="68" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="336" t="s">
+      <c r="B68" s="320" t="s">
         <v>192</v>
       </c>
-      <c r="C68" s="324"/>
-      <c r="D68" s="324"/>
-      <c r="E68" s="324"/>
-      <c r="F68" s="324"/>
-      <c r="G68" s="324"/>
-      <c r="H68" s="324"/>
-      <c r="I68" s="324"/>
-      <c r="J68" s="324"/>
-      <c r="K68" s="324"/>
-      <c r="L68" s="324"/>
-      <c r="M68" s="324"/>
-      <c r="N68" s="324"/>
-      <c r="O68" s="324"/>
-      <c r="P68" s="324"/>
-      <c r="Q68" s="337"/>
+      <c r="C68" s="321"/>
+      <c r="D68" s="321"/>
+      <c r="E68" s="321"/>
+      <c r="F68" s="321"/>
+      <c r="G68" s="321"/>
+      <c r="H68" s="321"/>
+      <c r="I68" s="321"/>
+      <c r="J68" s="321"/>
+      <c r="K68" s="321"/>
+      <c r="L68" s="321"/>
+      <c r="M68" s="321"/>
+      <c r="N68" s="321"/>
+      <c r="O68" s="321"/>
+      <c r="P68" s="321"/>
+      <c r="Q68" s="323"/>
     </row>
     <row r="69" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B69" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="302" t="s">
+      <c r="C69" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="302"/>
+      <c r="D69" s="303"/>
       <c r="E69" s="8" t="s">
         <v>3</v>
       </c>
@@ -57296,7 +57296,7 @@
       <c r="B70" s="219" t="s">
         <v>193</v>
       </c>
-      <c r="C70" s="330" t="s">
+      <c r="C70" s="317" t="s">
         <v>169</v>
       </c>
       <c r="D70" s="53" t="s">
@@ -57341,13 +57341,13 @@
       <c r="P70" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q70" s="341" t="s">
+      <c r="Q70" s="325" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B71" s="219"/>
-      <c r="C71" s="330"/>
+      <c r="C71" s="317"/>
       <c r="D71" s="53" t="s">
         <v>22</v>
       </c>
@@ -57390,36 +57390,36 @@
       <c r="P71" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="Q71" s="343"/>
+      <c r="Q71" s="331"/>
     </row>
     <row r="72" spans="2:18" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="336" t="s">
+      <c r="B72" s="320" t="s">
         <v>194</v>
       </c>
-      <c r="C72" s="324"/>
-      <c r="D72" s="324"/>
-      <c r="E72" s="324"/>
-      <c r="F72" s="324"/>
-      <c r="G72" s="324"/>
-      <c r="H72" s="324"/>
-      <c r="I72" s="324"/>
-      <c r="J72" s="324"/>
-      <c r="K72" s="324"/>
-      <c r="L72" s="324"/>
-      <c r="M72" s="324"/>
+      <c r="C72" s="321"/>
+      <c r="D72" s="321"/>
+      <c r="E72" s="321"/>
+      <c r="F72" s="321"/>
+      <c r="G72" s="321"/>
+      <c r="H72" s="321"/>
+      <c r="I72" s="321"/>
+      <c r="J72" s="321"/>
+      <c r="K72" s="321"/>
+      <c r="L72" s="321"/>
+      <c r="M72" s="321"/>
       <c r="N72" s="322"/>
-      <c r="O72" s="324"/>
-      <c r="P72" s="324"/>
-      <c r="Q72" s="337"/>
+      <c r="O72" s="321"/>
+      <c r="P72" s="321"/>
+      <c r="Q72" s="323"/>
     </row>
     <row r="73" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B73" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C73" s="302" t="s">
+      <c r="C73" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="302"/>
+      <c r="D73" s="303"/>
       <c r="E73" s="8" t="s">
         <v>3</v>
       </c>
@@ -57464,7 +57464,7 @@
       <c r="B74" s="219" t="s">
         <v>195</v>
       </c>
-      <c r="C74" s="330" t="s">
+      <c r="C74" s="317" t="s">
         <v>169</v>
       </c>
       <c r="D74" s="53" t="s">
@@ -57509,13 +57509,13 @@
       <c r="P74" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="Q74" s="341" t="s">
+      <c r="Q74" s="325" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="75" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="346"/>
-      <c r="C75" s="345"/>
+      <c r="B75" s="324"/>
+      <c r="C75" s="318"/>
       <c r="D75" s="90" t="s">
         <v>22</v>
       </c>
@@ -57558,15 +57558,15 @@
       <c r="P75" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="Q75" s="344"/>
+      <c r="Q75" s="326"/>
     </row>
     <row r="76" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="126"/>
       <c r="C76" s="126"/>
-      <c r="D76" s="317" t="s">
+      <c r="D76" s="319" t="s">
         <v>196</v>
       </c>
-      <c r="E76" s="317"/>
+      <c r="E76" s="319"/>
       <c r="F76" s="126"/>
       <c r="G76" s="126"/>
       <c r="H76" s="126"/>
@@ -57582,133 +57582,133 @@
       <c r="R76" s="126"/>
     </row>
     <row r="77" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="227" t="s">
+      <c r="B77" s="278" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="228"/>
-      <c r="D77" s="228"/>
-      <c r="E77" s="228"/>
-      <c r="F77" s="228"/>
-      <c r="G77" s="228"/>
-      <c r="H77" s="228"/>
-      <c r="I77" s="228"/>
-      <c r="J77" s="228"/>
-      <c r="K77" s="228"/>
-      <c r="L77" s="228"/>
-      <c r="M77" s="228"/>
-      <c r="N77" s="228"/>
-      <c r="O77" s="228"/>
-      <c r="P77" s="228"/>
-      <c r="Q77" s="228"/>
-      <c r="R77" s="229"/>
+      <c r="C77" s="279"/>
+      <c r="D77" s="279"/>
+      <c r="E77" s="279"/>
+      <c r="F77" s="279"/>
+      <c r="G77" s="279"/>
+      <c r="H77" s="279"/>
+      <c r="I77" s="279"/>
+      <c r="J77" s="279"/>
+      <c r="K77" s="279"/>
+      <c r="L77" s="279"/>
+      <c r="M77" s="279"/>
+      <c r="N77" s="279"/>
+      <c r="O77" s="279"/>
+      <c r="P77" s="279"/>
+      <c r="Q77" s="279"/>
+      <c r="R77" s="280"/>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B78" s="230" t="s">
+      <c r="B78" s="281" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="231"/>
-      <c r="D78" s="231"/>
-      <c r="E78" s="231"/>
-      <c r="F78" s="231"/>
-      <c r="G78" s="231"/>
-      <c r="H78" s="231"/>
-      <c r="I78" s="231"/>
-      <c r="J78" s="231"/>
-      <c r="K78" s="231"/>
-      <c r="L78" s="231"/>
-      <c r="M78" s="231"/>
-      <c r="N78" s="231"/>
-      <c r="O78" s="231"/>
-      <c r="P78" s="231"/>
-      <c r="Q78" s="231"/>
-      <c r="R78" s="232"/>
+      <c r="C78" s="282"/>
+      <c r="D78" s="282"/>
+      <c r="E78" s="282"/>
+      <c r="F78" s="282"/>
+      <c r="G78" s="282"/>
+      <c r="H78" s="282"/>
+      <c r="I78" s="282"/>
+      <c r="J78" s="282"/>
+      <c r="K78" s="282"/>
+      <c r="L78" s="282"/>
+      <c r="M78" s="282"/>
+      <c r="N78" s="282"/>
+      <c r="O78" s="282"/>
+      <c r="P78" s="282"/>
+      <c r="Q78" s="282"/>
+      <c r="R78" s="283"/>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B79" s="230"/>
-      <c r="C79" s="231"/>
-      <c r="D79" s="231"/>
-      <c r="E79" s="231"/>
-      <c r="F79" s="231"/>
-      <c r="G79" s="231"/>
-      <c r="H79" s="231"/>
-      <c r="I79" s="231"/>
-      <c r="J79" s="231"/>
-      <c r="K79" s="231"/>
-      <c r="L79" s="231"/>
-      <c r="M79" s="231"/>
-      <c r="N79" s="231"/>
-      <c r="O79" s="231"/>
-      <c r="P79" s="231"/>
-      <c r="Q79" s="231"/>
-      <c r="R79" s="232"/>
+      <c r="B79" s="281"/>
+      <c r="C79" s="282"/>
+      <c r="D79" s="282"/>
+      <c r="E79" s="282"/>
+      <c r="F79" s="282"/>
+      <c r="G79" s="282"/>
+      <c r="H79" s="282"/>
+      <c r="I79" s="282"/>
+      <c r="J79" s="282"/>
+      <c r="K79" s="282"/>
+      <c r="L79" s="282"/>
+      <c r="M79" s="282"/>
+      <c r="N79" s="282"/>
+      <c r="O79" s="282"/>
+      <c r="P79" s="282"/>
+      <c r="Q79" s="282"/>
+      <c r="R79" s="283"/>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B80" s="230"/>
-      <c r="C80" s="231"/>
-      <c r="D80" s="231"/>
-      <c r="E80" s="231"/>
-      <c r="F80" s="231"/>
-      <c r="G80" s="231"/>
-      <c r="H80" s="231"/>
-      <c r="I80" s="231"/>
-      <c r="J80" s="231"/>
-      <c r="K80" s="231"/>
-      <c r="L80" s="231"/>
-      <c r="M80" s="231"/>
-      <c r="N80" s="231"/>
-      <c r="O80" s="231"/>
-      <c r="P80" s="231"/>
-      <c r="Q80" s="231"/>
-      <c r="R80" s="232"/>
+      <c r="B80" s="281"/>
+      <c r="C80" s="282"/>
+      <c r="D80" s="282"/>
+      <c r="E80" s="282"/>
+      <c r="F80" s="282"/>
+      <c r="G80" s="282"/>
+      <c r="H80" s="282"/>
+      <c r="I80" s="282"/>
+      <c r="J80" s="282"/>
+      <c r="K80" s="282"/>
+      <c r="L80" s="282"/>
+      <c r="M80" s="282"/>
+      <c r="N80" s="282"/>
+      <c r="O80" s="282"/>
+      <c r="P80" s="282"/>
+      <c r="Q80" s="282"/>
+      <c r="R80" s="283"/>
     </row>
     <row r="81" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="233"/>
-      <c r="C81" s="234"/>
-      <c r="D81" s="234"/>
-      <c r="E81" s="234"/>
-      <c r="F81" s="234"/>
-      <c r="G81" s="234"/>
-      <c r="H81" s="234"/>
-      <c r="I81" s="234"/>
-      <c r="J81" s="234"/>
-      <c r="K81" s="234"/>
-      <c r="L81" s="234"/>
-      <c r="M81" s="234"/>
-      <c r="N81" s="234"/>
-      <c r="O81" s="234"/>
-      <c r="P81" s="234"/>
-      <c r="Q81" s="234"/>
-      <c r="R81" s="235"/>
+      <c r="B81" s="284"/>
+      <c r="C81" s="285"/>
+      <c r="D81" s="285"/>
+      <c r="E81" s="285"/>
+      <c r="F81" s="285"/>
+      <c r="G81" s="285"/>
+      <c r="H81" s="285"/>
+      <c r="I81" s="285"/>
+      <c r="J81" s="285"/>
+      <c r="K81" s="285"/>
+      <c r="L81" s="285"/>
+      <c r="M81" s="285"/>
+      <c r="N81" s="285"/>
+      <c r="O81" s="285"/>
+      <c r="P81" s="285"/>
+      <c r="Q81" s="285"/>
+      <c r="R81" s="286"/>
     </row>
     <row r="89" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B89" s="236" t="s">
+      <c r="B89" s="287" t="s">
         <v>197</v>
       </c>
-      <c r="C89" s="236"/>
-      <c r="D89" s="236"/>
-      <c r="E89" s="236"/>
-      <c r="F89" s="236"/>
-      <c r="G89" s="236"/>
-      <c r="H89" s="236"/>
-      <c r="I89" s="236"/>
-      <c r="J89" s="236"/>
-      <c r="K89" s="236"/>
-      <c r="L89" s="236"/>
-      <c r="M89" s="236"/>
-      <c r="N89" s="236"/>
-      <c r="O89" s="236"/>
-      <c r="P89" s="236"/>
-      <c r="Q89" s="236"/>
-      <c r="R89" s="236"/>
+      <c r="C89" s="287"/>
+      <c r="D89" s="287"/>
+      <c r="E89" s="287"/>
+      <c r="F89" s="287"/>
+      <c r="G89" s="287"/>
+      <c r="H89" s="287"/>
+      <c r="I89" s="287"/>
+      <c r="J89" s="287"/>
+      <c r="K89" s="287"/>
+      <c r="L89" s="287"/>
+      <c r="M89" s="287"/>
+      <c r="N89" s="287"/>
+      <c r="O89" s="287"/>
+      <c r="P89" s="287"/>
+      <c r="Q89" s="287"/>
+      <c r="R89" s="287"/>
     </row>
     <row r="90" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="302" t="s">
+      <c r="C90" s="303" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="302"/>
+      <c r="D90" s="303"/>
       <c r="E90" s="127" t="s">
         <v>128</v>
       </c>
@@ -57754,7 +57754,7 @@
       <c r="B91" s="220" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="237" t="s">
+      <c r="C91" s="228" t="s">
         <v>169</v>
       </c>
       <c r="D91" s="53" t="s">
@@ -57798,14 +57798,14 @@
       <c r="P91" s="53" t="s">
         <v>156</v>
       </c>
-      <c r="Q91" s="238" t="s">
+      <c r="Q91" s="236" t="s">
         <v>44</v>
       </c>
-      <c r="R91" s="238"/>
+      <c r="R91" s="236"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B92" s="220"/>
-      <c r="C92" s="237"/>
+      <c r="C92" s="228"/>
       <c r="D92" s="53" t="s">
         <v>22</v>
       </c>
@@ -57847,8 +57847,8 @@
       <c r="P92" s="53" t="s">
         <v>156</v>
       </c>
-      <c r="Q92" s="238"/>
-      <c r="R92" s="238"/>
+      <c r="Q92" s="236"/>
+      <c r="R92" s="236"/>
     </row>
     <row r="94" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
@@ -57872,82 +57872,82 @@
       <c r="R94" s="6"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B95" s="280" t="s">
+      <c r="B95" s="238" t="s">
         <v>33</v>
       </c>
-      <c r="C95" s="280"/>
-      <c r="D95" s="280"/>
-      <c r="E95" s="280"/>
-      <c r="F95" s="280"/>
-      <c r="G95" s="280"/>
-      <c r="H95" s="280"/>
-      <c r="I95" s="280"/>
-      <c r="J95" s="280"/>
-      <c r="K95" s="280"/>
-      <c r="L95" s="280"/>
-      <c r="M95" s="280"/>
-      <c r="N95" s="280"/>
-      <c r="O95" s="280"/>
-      <c r="P95" s="280"/>
-      <c r="Q95" s="280"/>
-      <c r="R95" s="280"/>
+      <c r="C95" s="238"/>
+      <c r="D95" s="238"/>
+      <c r="E95" s="238"/>
+      <c r="F95" s="238"/>
+      <c r="G95" s="238"/>
+      <c r="H95" s="238"/>
+      <c r="I95" s="238"/>
+      <c r="J95" s="238"/>
+      <c r="K95" s="238"/>
+      <c r="L95" s="238"/>
+      <c r="M95" s="238"/>
+      <c r="N95" s="238"/>
+      <c r="O95" s="238"/>
+      <c r="P95" s="238"/>
+      <c r="Q95" s="238"/>
+      <c r="R95" s="238"/>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B96" s="280"/>
-      <c r="C96" s="280"/>
-      <c r="D96" s="280"/>
-      <c r="E96" s="280"/>
-      <c r="F96" s="280"/>
-      <c r="G96" s="280"/>
-      <c r="H96" s="280"/>
-      <c r="I96" s="280"/>
-      <c r="J96" s="280"/>
-      <c r="K96" s="280"/>
-      <c r="L96" s="280"/>
-      <c r="M96" s="280"/>
-      <c r="N96" s="280"/>
-      <c r="O96" s="280"/>
-      <c r="P96" s="280"/>
-      <c r="Q96" s="280"/>
-      <c r="R96" s="280"/>
+      <c r="B96" s="238"/>
+      <c r="C96" s="238"/>
+      <c r="D96" s="238"/>
+      <c r="E96" s="238"/>
+      <c r="F96" s="238"/>
+      <c r="G96" s="238"/>
+      <c r="H96" s="238"/>
+      <c r="I96" s="238"/>
+      <c r="J96" s="238"/>
+      <c r="K96" s="238"/>
+      <c r="L96" s="238"/>
+      <c r="M96" s="238"/>
+      <c r="N96" s="238"/>
+      <c r="O96" s="238"/>
+      <c r="P96" s="238"/>
+      <c r="Q96" s="238"/>
+      <c r="R96" s="238"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B97" s="280"/>
-      <c r="C97" s="280"/>
-      <c r="D97" s="280"/>
-      <c r="E97" s="280"/>
-      <c r="F97" s="280"/>
-      <c r="G97" s="280"/>
-      <c r="H97" s="280"/>
-      <c r="I97" s="280"/>
-      <c r="J97" s="280"/>
-      <c r="K97" s="280"/>
-      <c r="L97" s="280"/>
-      <c r="M97" s="280"/>
-      <c r="N97" s="280"/>
-      <c r="O97" s="280"/>
-      <c r="P97" s="280"/>
-      <c r="Q97" s="280"/>
-      <c r="R97" s="280"/>
+      <c r="B97" s="238"/>
+      <c r="C97" s="238"/>
+      <c r="D97" s="238"/>
+      <c r="E97" s="238"/>
+      <c r="F97" s="238"/>
+      <c r="G97" s="238"/>
+      <c r="H97" s="238"/>
+      <c r="I97" s="238"/>
+      <c r="J97" s="238"/>
+      <c r="K97" s="238"/>
+      <c r="L97" s="238"/>
+      <c r="M97" s="238"/>
+      <c r="N97" s="238"/>
+      <c r="O97" s="238"/>
+      <c r="P97" s="238"/>
+      <c r="Q97" s="238"/>
+      <c r="R97" s="238"/>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B98" s="280"/>
-      <c r="C98" s="280"/>
-      <c r="D98" s="280"/>
-      <c r="E98" s="280"/>
-      <c r="F98" s="280"/>
-      <c r="G98" s="280"/>
-      <c r="H98" s="280"/>
-      <c r="I98" s="280"/>
-      <c r="J98" s="280"/>
-      <c r="K98" s="280"/>
-      <c r="L98" s="280"/>
-      <c r="M98" s="280"/>
-      <c r="N98" s="280"/>
-      <c r="O98" s="280"/>
-      <c r="P98" s="280"/>
-      <c r="Q98" s="280"/>
-      <c r="R98" s="280"/>
+      <c r="B98" s="238"/>
+      <c r="C98" s="238"/>
+      <c r="D98" s="238"/>
+      <c r="E98" s="238"/>
+      <c r="F98" s="238"/>
+      <c r="G98" s="238"/>
+      <c r="H98" s="238"/>
+      <c r="I98" s="238"/>
+      <c r="J98" s="238"/>
+      <c r="K98" s="238"/>
+      <c r="L98" s="238"/>
+      <c r="M98" s="238"/>
+      <c r="N98" s="238"/>
+      <c r="O98" s="238"/>
+      <c r="P98" s="238"/>
+      <c r="Q98" s="238"/>
+      <c r="R98" s="238"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="122"/>
@@ -57987,25 +57987,25 @@
       <c r="C108" s="28"/>
     </row>
     <row r="109" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B109" s="261" t="s">
-        <v>200</v>
-      </c>
-      <c r="C109" s="249"/>
-      <c r="D109" s="249"/>
-      <c r="E109" s="249"/>
-      <c r="F109" s="249"/>
-      <c r="G109" s="249"/>
-      <c r="H109" s="249"/>
-      <c r="I109" s="249"/>
-      <c r="J109" s="249"/>
-      <c r="K109" s="249"/>
-      <c r="L109" s="249"/>
-      <c r="M109" s="249"/>
-      <c r="N109" s="249"/>
-      <c r="O109" s="249"/>
-      <c r="P109" s="249"/>
-      <c r="Q109" s="249"/>
-      <c r="R109" s="249"/>
+      <c r="B109" s="256" t="s">
+        <v>200</v>
+      </c>
+      <c r="C109" s="223"/>
+      <c r="D109" s="223"/>
+      <c r="E109" s="223"/>
+      <c r="F109" s="223"/>
+      <c r="G109" s="223"/>
+      <c r="H109" s="223"/>
+      <c r="I109" s="223"/>
+      <c r="J109" s="223"/>
+      <c r="K109" s="223"/>
+      <c r="L109" s="223"/>
+      <c r="M109" s="223"/>
+      <c r="N109" s="223"/>
+      <c r="O109" s="223"/>
+      <c r="P109" s="223"/>
+      <c r="Q109" s="223"/>
+      <c r="R109" s="223"/>
     </row>
     <row r="110" spans="2:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B110" s="97" t="s">
@@ -58059,10 +58059,10 @@
       </c>
     </row>
     <row r="111" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B111" s="290" t="s">
+      <c r="B111" s="305" t="s">
         <v>99</v>
       </c>
-      <c r="C111" s="237" t="s">
+      <c r="C111" s="228" t="s">
         <v>169</v>
       </c>
       <c r="D111" s="53" t="s">
@@ -58114,8 +58114,8 @@
       </c>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B112" s="290"/>
-      <c r="C112" s="237"/>
+      <c r="B112" s="305"/>
+      <c r="C112" s="228"/>
       <c r="D112" s="53" t="s">
         <v>22</v>
       </c>
@@ -58165,10 +58165,10 @@
       </c>
     </row>
     <row r="113" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B113" s="290" t="s">
+      <c r="B113" s="305" t="s">
         <v>164</v>
       </c>
-      <c r="C113" s="237" t="s">
+      <c r="C113" s="228" t="s">
         <v>169</v>
       </c>
       <c r="D113" s="53" t="s">
@@ -58221,8 +58221,8 @@
       </c>
     </row>
     <row r="114" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B114" s="290"/>
-      <c r="C114" s="237"/>
+      <c r="B114" s="305"/>
+      <c r="C114" s="228"/>
       <c r="D114" s="53" t="s">
         <v>22</v>
       </c>
@@ -58274,6 +58274,57 @@
     </row>
   </sheetData>
   <mergeCells count="63">
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P22"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B9:P9"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="B109:R109"/>
+    <mergeCell ref="B56:Q56"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B40:P43"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="P34:Q36"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B68:Q68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="Q66:Q67"/>
+    <mergeCell ref="Q70:Q71"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="Q58:Q59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="B60:Q60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="Q62:Q63"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="Q74:Q75"/>
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="B113:B114"/>
     <mergeCell ref="C113:C114"/>
@@ -58282,61 +58333,10 @@
     <mergeCell ref="D76:E76"/>
     <mergeCell ref="B77:R77"/>
     <mergeCell ref="B78:R81"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="Q90:R90"/>
     <mergeCell ref="B91:B92"/>
     <mergeCell ref="C91:C92"/>
     <mergeCell ref="Q91:R92"/>
-    <mergeCell ref="Q74:Q75"/>
     <mergeCell ref="B95:R98"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="B60:Q60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="Q62:Q63"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="Q66:Q67"/>
-    <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="B64:Q64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="Q58:Q59"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B68:Q68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B40:P43"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="P34:Q36"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="B109:R109"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B9:P9"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B32:Q32"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P22"/>
   </mergeCells>
   <phoneticPr fontId="12" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58350,7 +58350,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B8:T40"/>
+  <dimension ref="B8:S40"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="19"/>
@@ -58379,24 +58379,24 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="261" t="s">
+      <c r="B8" s="256" t="s">
         <v>201</v>
       </c>
-      <c r="C8" s="249"/>
-      <c r="D8" s="249"/>
-      <c r="E8" s="249"/>
-      <c r="F8" s="249"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="249"/>
-      <c r="K8" s="249"/>
-      <c r="L8" s="249"/>
-      <c r="M8" s="249"/>
-      <c r="N8" s="249"/>
-      <c r="O8" s="249"/>
-      <c r="P8" s="249"/>
-      <c r="Q8" s="249"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="223"/>
+      <c r="H8" s="223"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="223"/>
+      <c r="K8" s="223"/>
+      <c r="L8" s="223"/>
+      <c r="M8" s="223"/>
+      <c r="N8" s="223"/>
+      <c r="O8" s="223"/>
+      <c r="P8" s="223"/>
+      <c r="Q8" s="223"/>
     </row>
     <row r="9" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B9" s="97" t="s">
@@ -58447,7 +58447,7 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="253" t="s">
+      <c r="B10" s="221" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="220" t="s">
@@ -58499,7 +58499,7 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="270"/>
+      <c r="B11" s="222"/>
       <c r="C11" s="220"/>
       <c r="D11" s="117" t="s">
         <v>22</v>
@@ -58547,25 +58547,25 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="261" t="s">
+      <c r="B12" s="256" t="s">
         <v>203</v>
       </c>
-      <c r="C12" s="249"/>
-      <c r="D12" s="249"/>
-      <c r="E12" s="249"/>
-      <c r="F12" s="249"/>
-      <c r="G12" s="249"/>
-      <c r="H12" s="249"/>
-      <c r="I12" s="249"/>
-      <c r="J12" s="249"/>
-      <c r="K12" s="249"/>
-      <c r="L12" s="249"/>
-      <c r="M12" s="249"/>
-      <c r="N12" s="249"/>
-      <c r="O12" s="249"/>
-      <c r="P12" s="249"/>
-      <c r="Q12" s="249"/>
-      <c r="R12" s="249"/>
+      <c r="C12" s="223"/>
+      <c r="D12" s="223"/>
+      <c r="E12" s="223"/>
+      <c r="F12" s="223"/>
+      <c r="G12" s="223"/>
+      <c r="H12" s="223"/>
+      <c r="I12" s="223"/>
+      <c r="J12" s="223"/>
+      <c r="K12" s="223"/>
+      <c r="L12" s="223"/>
+      <c r="M12" s="223"/>
+      <c r="N12" s="223"/>
+      <c r="O12" s="223"/>
+      <c r="P12" s="223"/>
+      <c r="Q12" s="223"/>
+      <c r="R12" s="223"/>
     </row>
     <row r="13" spans="2:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B13" s="97" t="s">
@@ -58734,24 +58734,24 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="351" t="s">
+      <c r="B16" s="349" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="352"/>
-      <c r="D16" s="352"/>
-      <c r="E16" s="352"/>
-      <c r="F16" s="352"/>
-      <c r="G16" s="352"/>
-      <c r="H16" s="352"/>
-      <c r="I16" s="352"/>
-      <c r="J16" s="352"/>
-      <c r="K16" s="352"/>
-      <c r="L16" s="352"/>
-      <c r="M16" s="352"/>
-      <c r="N16" s="352"/>
-      <c r="O16" s="352"/>
-      <c r="P16" s="352"/>
-      <c r="Q16" s="352"/>
+      <c r="C16" s="350"/>
+      <c r="D16" s="350"/>
+      <c r="E16" s="350"/>
+      <c r="F16" s="350"/>
+      <c r="G16" s="350"/>
+      <c r="H16" s="350"/>
+      <c r="I16" s="350"/>
+      <c r="J16" s="350"/>
+      <c r="K16" s="350"/>
+      <c r="L16" s="350"/>
+      <c r="M16" s="350"/>
+      <c r="N16" s="350"/>
+      <c r="O16" s="350"/>
+      <c r="P16" s="350"/>
+      <c r="Q16" s="350"/>
     </row>
     <row r="17" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="97" t="s">
@@ -58794,10 +58794,10 @@
       <c r="O17" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="349" t="s">
+      <c r="P17" s="347" t="s">
         <v>141</v>
       </c>
-      <c r="Q17" s="350"/>
+      <c r="Q17" s="348"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" s="220" t="s">
@@ -58896,22 +58896,22 @@
       <c r="Q19" s="53"/>
     </row>
     <row r="20" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="250" t="s">
+      <c r="B20" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C20" s="251"/>
-      <c r="D20" s="251"/>
-      <c r="E20" s="251"/>
-      <c r="F20" s="251"/>
-      <c r="G20" s="251"/>
-      <c r="H20" s="251"/>
-      <c r="I20" s="251"/>
-      <c r="J20" s="251"/>
-      <c r="K20" s="251"/>
-      <c r="L20" s="251"/>
-      <c r="M20" s="251"/>
-      <c r="N20" s="251"/>
-      <c r="O20" s="251"/>
+      <c r="C20" s="230"/>
+      <c r="D20" s="230"/>
+      <c r="E20" s="230"/>
+      <c r="F20" s="230"/>
+      <c r="G20" s="230"/>
+      <c r="H20" s="230"/>
+      <c r="I20" s="230"/>
+      <c r="J20" s="230"/>
+      <c r="K20" s="230"/>
+      <c r="L20" s="230"/>
+      <c r="M20" s="230"/>
+      <c r="N20" s="230"/>
+      <c r="O20" s="230"/>
       <c r="P20" s="211"/>
     </row>
     <row r="21" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -58955,8 +58955,8 @@
       <c r="O21" s="120" t="s">
         <v>141</v>
       </c>
-      <c r="P21" s="347"/>
-      <c r="Q21" s="348"/>
+      <c r="P21" s="351"/>
+      <c r="Q21" s="352"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="220" t="s">
@@ -59051,22 +59051,22 @@
       <c r="P23" s="209"/>
     </row>
     <row r="24" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="261" t="s">
+      <c r="B24" s="256" t="s">
         <v>213</v>
       </c>
-      <c r="C24" s="249"/>
-      <c r="D24" s="249"/>
-      <c r="E24" s="249"/>
-      <c r="F24" s="249"/>
-      <c r="G24" s="249"/>
-      <c r="H24" s="249"/>
-      <c r="I24" s="249"/>
-      <c r="J24" s="249"/>
-      <c r="K24" s="249"/>
-      <c r="L24" s="249"/>
-      <c r="M24" s="249"/>
-      <c r="N24" s="249"/>
-      <c r="O24" s="249"/>
+      <c r="C24" s="223"/>
+      <c r="D24" s="223"/>
+      <c r="E24" s="223"/>
+      <c r="F24" s="223"/>
+      <c r="G24" s="223"/>
+      <c r="H24" s="223"/>
+      <c r="I24" s="223"/>
+      <c r="J24" s="223"/>
+      <c r="K24" s="223"/>
+      <c r="L24" s="223"/>
+      <c r="M24" s="223"/>
+      <c r="N24" s="223"/>
+      <c r="O24" s="223"/>
       <c r="P24" s="61"/>
     </row>
     <row r="25" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
@@ -59227,78 +59227,78 @@
       <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B30" s="221" t="s">
+      <c r="B30" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="222"/>
-      <c r="D30" s="222"/>
-      <c r="E30" s="222"/>
-      <c r="F30" s="222"/>
-      <c r="G30" s="222"/>
-      <c r="H30" s="222"/>
-      <c r="I30" s="222"/>
-      <c r="J30" s="222"/>
-      <c r="K30" s="222"/>
-      <c r="L30" s="222"/>
-      <c r="M30" s="222"/>
-      <c r="N30" s="222"/>
-      <c r="O30" s="222"/>
-      <c r="P30" s="222"/>
-      <c r="Q30" s="223"/>
+      <c r="C30" s="240"/>
+      <c r="D30" s="240"/>
+      <c r="E30" s="240"/>
+      <c r="F30" s="240"/>
+      <c r="G30" s="240"/>
+      <c r="H30" s="240"/>
+      <c r="I30" s="240"/>
+      <c r="J30" s="240"/>
+      <c r="K30" s="240"/>
+      <c r="L30" s="240"/>
+      <c r="M30" s="240"/>
+      <c r="N30" s="240"/>
+      <c r="O30" s="240"/>
+      <c r="P30" s="240"/>
+      <c r="Q30" s="241"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="221"/>
-      <c r="C31" s="222"/>
-      <c r="D31" s="222"/>
-      <c r="E31" s="222"/>
-      <c r="F31" s="222"/>
-      <c r="G31" s="222"/>
-      <c r="H31" s="222"/>
-      <c r="I31" s="222"/>
-      <c r="J31" s="222"/>
-      <c r="K31" s="222"/>
-      <c r="L31" s="222"/>
-      <c r="M31" s="222"/>
-      <c r="N31" s="222"/>
-      <c r="O31" s="222"/>
-      <c r="P31" s="222"/>
-      <c r="Q31" s="223"/>
+      <c r="B31" s="239"/>
+      <c r="C31" s="240"/>
+      <c r="D31" s="240"/>
+      <c r="E31" s="240"/>
+      <c r="F31" s="240"/>
+      <c r="G31" s="240"/>
+      <c r="H31" s="240"/>
+      <c r="I31" s="240"/>
+      <c r="J31" s="240"/>
+      <c r="K31" s="240"/>
+      <c r="L31" s="240"/>
+      <c r="M31" s="240"/>
+      <c r="N31" s="240"/>
+      <c r="O31" s="240"/>
+      <c r="P31" s="240"/>
+      <c r="Q31" s="241"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B32" s="221"/>
-      <c r="C32" s="222"/>
-      <c r="D32" s="222"/>
-      <c r="E32" s="222"/>
-      <c r="F32" s="222"/>
-      <c r="G32" s="222"/>
-      <c r="H32" s="222"/>
-      <c r="I32" s="222"/>
-      <c r="J32" s="222"/>
-      <c r="K32" s="222"/>
-      <c r="L32" s="222"/>
-      <c r="M32" s="222"/>
-      <c r="N32" s="222"/>
-      <c r="O32" s="222"/>
-      <c r="P32" s="222"/>
-      <c r="Q32" s="223"/>
+      <c r="B32" s="239"/>
+      <c r="C32" s="240"/>
+      <c r="D32" s="240"/>
+      <c r="E32" s="240"/>
+      <c r="F32" s="240"/>
+      <c r="G32" s="240"/>
+      <c r="H32" s="240"/>
+      <c r="I32" s="240"/>
+      <c r="J32" s="240"/>
+      <c r="K32" s="240"/>
+      <c r="L32" s="240"/>
+      <c r="M32" s="240"/>
+      <c r="N32" s="240"/>
+      <c r="O32" s="240"/>
+      <c r="P32" s="240"/>
+      <c r="Q32" s="241"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="224"/>
-      <c r="C33" s="225"/>
-      <c r="D33" s="225"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="225"/>
-      <c r="G33" s="225"/>
-      <c r="H33" s="225"/>
-      <c r="I33" s="225"/>
-      <c r="J33" s="225"/>
-      <c r="K33" s="225"/>
-      <c r="L33" s="225"/>
-      <c r="M33" s="225"/>
-      <c r="N33" s="225"/>
-      <c r="O33" s="225"/>
-      <c r="P33" s="225"/>
-      <c r="Q33" s="226"/>
+      <c r="B33" s="242"/>
+      <c r="C33" s="243"/>
+      <c r="D33" s="243"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="243"/>
+      <c r="I33" s="243"/>
+      <c r="J33" s="243"/>
+      <c r="K33" s="243"/>
+      <c r="L33" s="243"/>
+      <c r="M33" s="243"/>
+      <c r="N33" s="243"/>
+      <c r="O33" s="243"/>
+      <c r="P33" s="243"/>
+      <c r="Q33" s="244"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B34" s="35"/>
@@ -59428,11 +59428,15 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B20:O20"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B30:Q33"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B24:O24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="P21:Q21"/>
     <mergeCell ref="B8:Q8"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C17:D17"/>
@@ -59442,15 +59446,11 @@
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="P17:Q17"/>
     <mergeCell ref="B16:Q16"/>
-    <mergeCell ref="B30:Q33"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B24:O24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="B20:O20"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -59637,10 +59637,10 @@
       <c r="B10" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="353" t="s">
+      <c r="C10" s="365" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="353"/>
+      <c r="D10" s="365"/>
       <c r="E10" s="15" t="s">
         <v>3</v>
       </c>
@@ -59679,10 +59679,10 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="354" t="s">
-        <v>215</v>
-      </c>
-      <c r="C11" s="357" t="s">
+      <c r="B11" s="361" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="363" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -59728,8 +59728,8 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="355"/>
-      <c r="C12" s="357"/>
+      <c r="B12" s="366"/>
+      <c r="C12" s="363"/>
       <c r="D12" s="45" t="s">
         <v>22</v>
       </c>
@@ -59773,8 +59773,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="355"/>
-      <c r="C13" s="357" t="s">
+      <c r="B13" s="366"/>
+      <c r="C13" s="363" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="45" t="s">
@@ -59820,8 +59820,8 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="355"/>
-      <c r="C14" s="357"/>
+      <c r="B14" s="366"/>
+      <c r="C14" s="363"/>
       <c r="D14" s="45" t="s">
         <v>22</v>
       </c>
@@ -59865,8 +59865,8 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="355"/>
-      <c r="C15" s="357" t="s">
+      <c r="B15" s="366"/>
+      <c r="C15" s="363" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="45" t="s">
@@ -59912,8 +59912,8 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="355"/>
-      <c r="C16" s="357"/>
+      <c r="B16" s="366"/>
+      <c r="C16" s="363"/>
       <c r="D16" s="45" t="s">
         <v>22</v>
       </c>
@@ -59957,8 +59957,8 @@
       </c>
     </row>
     <row r="17" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="355"/>
-      <c r="C17" s="357" t="s">
+      <c r="B17" s="366"/>
+      <c r="C17" s="363" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -60004,8 +60004,8 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="355"/>
-      <c r="C18" s="357"/>
+      <c r="B18" s="366"/>
+      <c r="C18" s="363"/>
       <c r="D18" s="45" t="s">
         <v>22</v>
       </c>
@@ -60049,8 +60049,8 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="355"/>
-      <c r="C19" s="357" t="s">
+      <c r="B19" s="366"/>
+      <c r="C19" s="363" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="45" t="s">
@@ -60096,8 +60096,8 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="356"/>
-      <c r="C20" s="357"/>
+      <c r="B20" s="362"/>
+      <c r="C20" s="363"/>
       <c r="D20" s="45" t="s">
         <v>22</v>
       </c>
@@ -60141,10 +60141,10 @@
       </c>
     </row>
     <row r="21" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="354" t="s">
+      <c r="B21" s="361" t="s">
         <v>220</v>
       </c>
-      <c r="C21" s="357" t="s">
+      <c r="C21" s="363" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="45" t="s">
@@ -60190,8 +60190,8 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="356"/>
-      <c r="C22" s="357"/>
+      <c r="B22" s="362"/>
+      <c r="C22" s="363"/>
       <c r="D22" s="45" t="s">
         <v>22</v>
       </c>
@@ -60235,10 +60235,10 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="354" t="s">
+      <c r="B23" s="361" t="s">
         <v>221</v>
       </c>
-      <c r="C23" s="357" t="s">
+      <c r="C23" s="363" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="45" t="s">
@@ -60284,8 +60284,8 @@
       </c>
     </row>
     <row r="24" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="356"/>
-      <c r="C24" s="357"/>
+      <c r="B24" s="362"/>
+      <c r="C24" s="363"/>
       <c r="D24" s="45" t="s">
         <v>22</v>
       </c>
@@ -60423,8 +60423,8 @@
       </c>
     </row>
     <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="346"/>
-      <c r="C27" s="366"/>
+      <c r="B27" s="324"/>
+      <c r="C27" s="364"/>
       <c r="D27" s="84" t="s">
         <v>17</v>
       </c>
@@ -60484,96 +60484,103 @@
       <c r="O28" s="28"/>
     </row>
     <row r="29" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="358" t="s">
+      <c r="B29" s="353" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="359"/>
-      <c r="D29" s="359"/>
-      <c r="E29" s="359"/>
-      <c r="F29" s="359"/>
-      <c r="G29" s="359"/>
-      <c r="H29" s="359"/>
-      <c r="I29" s="359"/>
-      <c r="J29" s="359"/>
-      <c r="K29" s="359"/>
-      <c r="L29" s="359"/>
-      <c r="M29" s="359"/>
-      <c r="N29" s="359"/>
-      <c r="O29" s="359"/>
-      <c r="P29" s="360"/>
+      <c r="C29" s="354"/>
+      <c r="D29" s="354"/>
+      <c r="E29" s="354"/>
+      <c r="F29" s="354"/>
+      <c r="G29" s="354"/>
+      <c r="H29" s="354"/>
+      <c r="I29" s="354"/>
+      <c r="J29" s="354"/>
+      <c r="K29" s="354"/>
+      <c r="L29" s="354"/>
+      <c r="M29" s="354"/>
+      <c r="N29" s="354"/>
+      <c r="O29" s="354"/>
+      <c r="P29" s="355"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="361" t="s">
+      <c r="B30" s="356" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="222"/>
-      <c r="D30" s="222"/>
-      <c r="E30" s="222"/>
-      <c r="F30" s="222"/>
-      <c r="G30" s="222"/>
-      <c r="H30" s="222"/>
-      <c r="I30" s="222"/>
-      <c r="J30" s="222"/>
-      <c r="K30" s="222"/>
-      <c r="L30" s="222"/>
-      <c r="M30" s="222"/>
-      <c r="N30" s="222"/>
-      <c r="O30" s="222"/>
-      <c r="P30" s="362"/>
+      <c r="C30" s="240"/>
+      <c r="D30" s="240"/>
+      <c r="E30" s="240"/>
+      <c r="F30" s="240"/>
+      <c r="G30" s="240"/>
+      <c r="H30" s="240"/>
+      <c r="I30" s="240"/>
+      <c r="J30" s="240"/>
+      <c r="K30" s="240"/>
+      <c r="L30" s="240"/>
+      <c r="M30" s="240"/>
+      <c r="N30" s="240"/>
+      <c r="O30" s="240"/>
+      <c r="P30" s="357"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="361"/>
-      <c r="C31" s="222"/>
-      <c r="D31" s="222"/>
-      <c r="E31" s="222"/>
-      <c r="F31" s="222"/>
-      <c r="G31" s="222"/>
-      <c r="H31" s="222"/>
-      <c r="I31" s="222"/>
-      <c r="J31" s="222"/>
-      <c r="K31" s="222"/>
-      <c r="L31" s="222"/>
-      <c r="M31" s="222"/>
-      <c r="N31" s="222"/>
-      <c r="O31" s="222"/>
-      <c r="P31" s="362"/>
+      <c r="B31" s="356"/>
+      <c r="C31" s="240"/>
+      <c r="D31" s="240"/>
+      <c r="E31" s="240"/>
+      <c r="F31" s="240"/>
+      <c r="G31" s="240"/>
+      <c r="H31" s="240"/>
+      <c r="I31" s="240"/>
+      <c r="J31" s="240"/>
+      <c r="K31" s="240"/>
+      <c r="L31" s="240"/>
+      <c r="M31" s="240"/>
+      <c r="N31" s="240"/>
+      <c r="O31" s="240"/>
+      <c r="P31" s="357"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="361"/>
-      <c r="C32" s="222"/>
-      <c r="D32" s="222"/>
-      <c r="E32" s="222"/>
-      <c r="F32" s="222"/>
-      <c r="G32" s="222"/>
-      <c r="H32" s="222"/>
-      <c r="I32" s="222"/>
-      <c r="J32" s="222"/>
-      <c r="K32" s="222"/>
-      <c r="L32" s="222"/>
-      <c r="M32" s="222"/>
-      <c r="N32" s="222"/>
-      <c r="O32" s="222"/>
-      <c r="P32" s="362"/>
+      <c r="B32" s="356"/>
+      <c r="C32" s="240"/>
+      <c r="D32" s="240"/>
+      <c r="E32" s="240"/>
+      <c r="F32" s="240"/>
+      <c r="G32" s="240"/>
+      <c r="H32" s="240"/>
+      <c r="I32" s="240"/>
+      <c r="J32" s="240"/>
+      <c r="K32" s="240"/>
+      <c r="L32" s="240"/>
+      <c r="M32" s="240"/>
+      <c r="N32" s="240"/>
+      <c r="O32" s="240"/>
+      <c r="P32" s="357"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="363"/>
-      <c r="C33" s="364"/>
-      <c r="D33" s="364"/>
-      <c r="E33" s="364"/>
-      <c r="F33" s="364"/>
-      <c r="G33" s="364"/>
-      <c r="H33" s="364"/>
-      <c r="I33" s="364"/>
-      <c r="J33" s="364"/>
-      <c r="K33" s="364"/>
-      <c r="L33" s="364"/>
-      <c r="M33" s="364"/>
-      <c r="N33" s="364"/>
-      <c r="O33" s="364"/>
-      <c r="P33" s="365"/>
+      <c r="B33" s="358"/>
+      <c r="C33" s="359"/>
+      <c r="D33" s="359"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
+      <c r="G33" s="359"/>
+      <c r="H33" s="359"/>
+      <c r="I33" s="359"/>
+      <c r="J33" s="359"/>
+      <c r="K33" s="359"/>
+      <c r="L33" s="359"/>
+      <c r="M33" s="359"/>
+      <c r="N33" s="359"/>
+      <c r="O33" s="359"/>
+      <c r="P33" s="360"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="B29:P29"/>
     <mergeCell ref="B30:P33"/>
     <mergeCell ref="B21:B22"/>
@@ -60582,13 +60589,6 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="landscape" r:id="rId1"/>
@@ -60597,6 +60597,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BF631F92D611394D900040A4BC36CE07" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="711a2ec75ffd0c152903cfa2dedf38be">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8bf418b7-79e0-4993-aa07-d31c53a64380" xmlns:ns3="268ad1c4-fabf-4dd0-b894-8fd5403102c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0628c710989f2757c815e19c03677863" ns2:_="" ns3:_="">
     <xsd:import namespace="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
@@ -60819,27 +60839,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
+    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8bf418b7-79e0-4993-aa07-d31c53a64380">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="268ad1c4-fabf-4dd0-b894-8fd5403102c0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A722593-7143-4ACD-9A00-2A0E70214590}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -60856,23 +60875,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AAFA3EB-B8AB-4135-B122-0B0233A6C07D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900DAED1-575B-462E-9521-61C8D8B6DAE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8bf418b7-79e0-4993-aa07-d31c53a64380"/>
-    <ds:schemaRef ds:uri="268ad1c4-fabf-4dd0-b894-8fd5403102c0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>